--- a/dev_stuffs/2玩家数值模型.xlsx
+++ b/dev_stuffs/2玩家数值模型.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12044\Documents\EX\PCL\.minecraft\versions\Palmon\dev_stuffs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD0331D-59CD-4F1E-BD8D-9ED91D960274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C222CE-9407-4DA8-B9B7-CA8675085AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="2100" windowWidth="19200" windowHeight="11260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="4920" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="伤害计算" sheetId="1" r:id="rId1"/>
@@ -740,39 +740,96 @@
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="5" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="13" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="4" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="14" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="5" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="15" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -801,63 +858,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="13" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="4" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="14" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="5" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="15" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1133,25 +1133,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
+      <c r="B1" s="41"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1272,88 +1272,88 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="11" max="11" width="9.453125" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125"/>
-    <col min="13" max="13" width="9.26953125" customWidth="1"/>
-    <col min="15" max="15" width="11.6328125" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
+    <col min="12" max="12" width="12.625"/>
+    <col min="13" max="13" width="9.25" customWidth="1"/>
+    <col min="15" max="15" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="H1" s="35" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="H1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="H3" s="42" t="s">
+      <c r="B3" s="50"/>
+      <c r="H3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="42"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="I3" s="50"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A4" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="H4" s="42" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="H4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A5" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="H5" s="39" t="s">
+      <c r="B5" s="51"/>
+      <c r="H5" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39" t="s">
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1369,8 +1369,8 @@
       <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="39"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="45"/>
       <c r="J6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1390,8 +1390,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="36">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A7" s="42">
         <v>1</v>
       </c>
       <c r="B7" s="3">
@@ -1405,7 +1405,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="H7" s="36">
+      <c r="H7" s="42">
         <v>1</v>
       </c>
       <c r="I7" s="3">
@@ -1436,8 +1436,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A8" s="43"/>
       <c r="B8" s="3">
         <v>1</v>
       </c>
@@ -1452,7 +1452,7 @@
         <f t="shared" ref="E8:E27" si="2">D8-D7</f>
         <v>1</v>
       </c>
-      <c r="H8" s="37"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="3">
         <f t="shared" ref="I8:I27" si="3">D8</f>
         <v>11</v>
@@ -1481,8 +1481,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A9" s="43"/>
       <c r="B9" s="3">
         <v>1</v>
       </c>
@@ -1497,7 +1497,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H9" s="37"/>
+      <c r="H9" s="43"/>
       <c r="I9" s="3">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -1526,8 +1526,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="38"/>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="44"/>
       <c r="B10" s="3">
         <v>2</v>
       </c>
@@ -1542,7 +1542,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H10" s="38"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -1571,8 +1571,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="36">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="42">
         <v>2</v>
       </c>
       <c r="B11" s="3">
@@ -1589,7 +1589,7 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="42">
         <v>2</v>
       </c>
       <c r="I11" s="3">
@@ -1620,8 +1620,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="43"/>
       <c r="B12" s="3">
         <v>4</v>
       </c>
@@ -1636,7 +1636,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H12" s="37"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="3">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -1665,8 +1665,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="43"/>
       <c r="B13" s="3">
         <v>4</v>
       </c>
@@ -1681,7 +1681,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="3">
         <f t="shared" si="3"/>
         <v>34</v>
@@ -1710,8 +1710,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="38"/>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="44"/>
       <c r="B14" s="3">
         <v>4</v>
       </c>
@@ -1726,7 +1726,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H14" s="38"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="3">
         <f t="shared" si="3"/>
         <v>38</v>
@@ -1755,8 +1755,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="36">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" s="42">
         <v>3</v>
       </c>
       <c r="B15" s="3">
@@ -1773,7 +1773,7 @@
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="42">
         <v>3</v>
       </c>
       <c r="I15" s="3">
@@ -1804,8 +1804,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" s="43"/>
       <c r="B16" s="3">
         <v>9</v>
       </c>
@@ -1820,7 +1820,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H16" s="37"/>
+      <c r="H16" s="43"/>
       <c r="I16" s="3">
         <f t="shared" si="3"/>
         <v>91</v>
@@ -1849,8 +1849,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="37"/>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" s="43"/>
       <c r="B17" s="3">
         <v>9</v>
       </c>
@@ -1865,7 +1865,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H17" s="37"/>
+      <c r="H17" s="43"/>
       <c r="I17" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
@@ -1894,8 +1894,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" s="43"/>
       <c r="B18" s="3">
         <v>9</v>
       </c>
@@ -1910,7 +1910,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H18" s="37"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="3">
         <f t="shared" si="3"/>
         <v>109</v>
@@ -1939,8 +1939,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A19" s="43"/>
       <c r="B19" s="3">
         <v>9</v>
       </c>
@@ -1955,7 +1955,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H19" s="37"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="3">
         <f t="shared" si="3"/>
         <v>118</v>
@@ -1984,8 +1984,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A20" s="44"/>
       <c r="B20" s="3">
         <v>9</v>
       </c>
@@ -2000,7 +2000,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H20" s="38"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="3">
         <f t="shared" si="3"/>
         <v>127</v>
@@ -2029,8 +2029,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="36">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" s="42">
         <v>4</v>
       </c>
       <c r="B21" s="3">
@@ -2047,7 +2047,7 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="42">
         <v>4</v>
       </c>
       <c r="I21" s="3">
@@ -2078,8 +2078,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" s="43"/>
       <c r="B22" s="3">
         <v>16</v>
       </c>
@@ -2094,7 +2094,7 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="H22" s="37"/>
+      <c r="H22" s="43"/>
       <c r="I22" s="3">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -2123,8 +2123,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" s="44"/>
       <c r="B23" s="3">
         <v>16</v>
       </c>
@@ -2139,7 +2139,7 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="H23" s="38"/>
+      <c r="H23" s="44"/>
       <c r="I23" s="3">
         <f t="shared" si="3"/>
         <v>266</v>
@@ -2168,8 +2168,8 @@
         <v>266</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="36">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" s="42">
         <v>5</v>
       </c>
       <c r="B24" s="3">
@@ -2186,7 +2186,7 @@
         <f t="shared" si="2"/>
         <v>254</v>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="42">
         <v>5</v>
       </c>
       <c r="I24" s="3">
@@ -2217,8 +2217,8 @@
         <v>520</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" s="43"/>
       <c r="B25" s="3">
         <v>31</v>
       </c>
@@ -2233,7 +2233,7 @@
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="H25" s="37"/>
+      <c r="H25" s="43"/>
       <c r="I25" s="3">
         <f t="shared" si="3"/>
         <v>568</v>
@@ -2262,8 +2262,8 @@
         <v>568</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" s="43"/>
       <c r="B26" s="3">
         <v>32</v>
       </c>
@@ -2278,7 +2278,7 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="3">
         <f t="shared" si="3"/>
         <v>618</v>
@@ -2307,8 +2307,8 @@
         <v>618</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" s="44"/>
       <c r="B27" s="3">
         <v>35</v>
       </c>
@@ -2323,7 +2323,7 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="H27" s="38"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="3">
         <f t="shared" si="3"/>
         <v>710</v>
@@ -2352,55 +2352,55 @@
         <v>710</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
       <c r="D30" s="9"/>
     </row>
-    <row r="32" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="H32" s="34" t="s">
+      <c r="H32" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-    </row>
-    <row r="33" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+    </row>
+    <row r="33" spans="1:14" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H34" s="40" t="s">
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H34" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="I34" s="40"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H35" s="40" t="s">
+      <c r="I34" s="46"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H35" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="H36" s="1" t="s">
         <v>14</v>
       </c>
@@ -2423,8 +2423,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H37" s="36">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H37" s="42">
         <v>1</v>
       </c>
       <c r="I37" s="6">
@@ -2447,8 +2447,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H38" s="37"/>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H38" s="43"/>
       <c r="I38" s="6">
         <v>15</v>
       </c>
@@ -2470,8 +2470,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H39" s="37"/>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H39" s="43"/>
       <c r="I39" s="6">
         <v>15</v>
       </c>
@@ -2493,8 +2493,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H40" s="38"/>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H40" s="44"/>
       <c r="I40" s="6">
         <v>15</v>
       </c>
@@ -2516,8 +2516,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H41" s="36">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H41" s="42">
         <v>2</v>
       </c>
       <c r="I41" s="6">
@@ -2541,8 +2541,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H42" s="37"/>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H42" s="43"/>
       <c r="I42" s="6">
         <v>35</v>
       </c>
@@ -2564,8 +2564,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H43" s="37"/>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H43" s="43"/>
       <c r="I43" s="6">
         <v>35</v>
       </c>
@@ -2587,8 +2587,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H44" s="38"/>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H44" s="44"/>
       <c r="I44" s="6">
         <v>35</v>
       </c>
@@ -2610,8 +2610,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H45" s="36">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H45" s="42">
         <v>3</v>
       </c>
       <c r="I45" s="6">
@@ -2635,8 +2635,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H46" s="37"/>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H46" s="43"/>
       <c r="I46" s="6">
         <v>80</v>
       </c>
@@ -2658,8 +2658,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H47" s="37"/>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H47" s="43"/>
       <c r="I47" s="6">
         <v>80</v>
       </c>
@@ -2681,8 +2681,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H48" s="37"/>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="H48" s="43"/>
       <c r="I48" s="6">
         <v>80</v>
       </c>
@@ -2704,8 +2704,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H49" s="37"/>
+    <row r="49" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H49" s="43"/>
       <c r="I49" s="6">
         <v>80</v>
       </c>
@@ -2727,8 +2727,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H50" s="38"/>
+    <row r="50" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H50" s="44"/>
       <c r="I50" s="6">
         <v>80</v>
       </c>
@@ -2750,8 +2750,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H51" s="36">
+    <row r="51" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H51" s="42">
         <v>4</v>
       </c>
       <c r="I51" s="6">
@@ -2775,8 +2775,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H52" s="37"/>
+    <row r="52" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H52" s="43"/>
       <c r="I52" s="6">
         <v>120</v>
       </c>
@@ -2798,8 +2798,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H53" s="38"/>
+    <row r="53" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H53" s="44"/>
       <c r="I53" s="6">
         <v>120</v>
       </c>
@@ -2821,8 +2821,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H54" s="36">
+    <row r="54" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H54" s="42">
         <v>5</v>
       </c>
       <c r="I54" s="6">
@@ -2846,8 +2846,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H55" s="37"/>
+    <row r="55" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H55" s="43"/>
       <c r="I55" s="6">
         <v>200</v>
       </c>
@@ -2869,8 +2869,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H56" s="37"/>
+    <row r="56" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H56" s="43"/>
       <c r="I56" s="6">
         <v>200</v>
       </c>
@@ -2892,8 +2892,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H57" s="38"/>
+    <row r="57" spans="8:14" x14ac:dyDescent="0.15">
+      <c r="H57" s="44"/>
       <c r="I57" s="6">
         <v>200</v>
       </c>
@@ -2917,20 +2917,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="H45:H50"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:L35"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="H15:H20"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:L5"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="H1:L2"/>
     <mergeCell ref="H32:N33"/>
@@ -2946,6 +2932,20 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H45:H50"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:L35"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="H15:H20"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:L5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3054,61 +3054,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U93"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="40" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="55" t="s">
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A3" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -3120,7 +3120,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -3144,7 +3144,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3186,35 +3186,35 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A7" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="39" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="55" t="s">
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="40" t="s">
+      <c r="L7" s="52"/>
+      <c r="M7" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>41</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="25">
         <v>1</v>
       </c>
@@ -3317,11 +3317,11 @@
         <f>O9*(M9-Q9)</f>
         <v>12.64</v>
       </c>
-      <c r="S9" s="44" t="s">
+      <c r="S9" s="63" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A10" s="25">
         <v>2</v>
       </c>
@@ -3368,9 +3368,9 @@
         <f t="shared" ref="R10:R29" si="0">O10*(M10-Q10)</f>
         <v>14.4</v>
       </c>
-      <c r="S10" s="45"/>
-    </row>
-    <row r="11" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S10" s="64"/>
+    </row>
+    <row r="11" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A11" s="25">
         <v>3</v>
       </c>
@@ -3417,9 +3417,9 @@
         <f t="shared" si="0"/>
         <v>16.16</v>
       </c>
-      <c r="S11" s="45"/>
-    </row>
-    <row r="12" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S11" s="64"/>
+    </row>
+    <row r="12" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13">
         <v>4</v>
       </c>
@@ -3466,14 +3466,14 @@
         <f t="shared" si="0"/>
         <v>21.76</v>
       </c>
-      <c r="S12" s="46" t="s">
+      <c r="S12" s="65" t="s">
         <v>79</v>
       </c>
       <c r="T12" s="28" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A13" s="13">
         <v>5</v>
       </c>
@@ -3520,7 +3520,7 @@
         <f t="shared" si="0"/>
         <v>35.28</v>
       </c>
-      <c r="S13" s="47"/>
+      <c r="S13" s="66"/>
       <c r="T13" s="28" t="s">
         <v>84</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="13">
         <v>6</v>
       </c>
@@ -3575,7 +3575,7 @@
         <f t="shared" si="0"/>
         <v>41.832000000000001</v>
       </c>
-      <c r="S14" s="47"/>
+      <c r="S14" s="66"/>
       <c r="T14" s="28" t="s">
         <v>85</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13">
         <v>7</v>
       </c>
@@ -3630,7 +3630,7 @@
         <f t="shared" si="0"/>
         <v>48.384</v>
       </c>
-      <c r="S15" s="47"/>
+      <c r="S15" s="66"/>
       <c r="T15" s="28" t="s">
         <v>86</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13">
         <v>8</v>
       </c>
@@ -3685,12 +3685,12 @@
         <f t="shared" si="0"/>
         <v>55.103999999999999</v>
       </c>
-      <c r="S16" s="47"/>
+      <c r="S16" s="66"/>
       <c r="U16" s="28" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A17" s="16">
         <v>9</v>
       </c>
@@ -3737,14 +3737,14 @@
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="S17" s="48" t="s">
+      <c r="S17" s="67" t="s">
         <v>80</v>
       </c>
       <c r="T17" s="29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A18" s="16">
         <v>10</v>
       </c>
@@ -3791,12 +3791,12 @@
         <f t="shared" si="0"/>
         <v>123.2</v>
       </c>
-      <c r="S18" s="49"/>
+      <c r="S18" s="68"/>
       <c r="T18" s="29" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A19" s="16">
         <v>11</v>
       </c>
@@ -3843,12 +3843,12 @@
         <f t="shared" si="0"/>
         <v>136.4</v>
       </c>
-      <c r="S19" s="49"/>
+      <c r="S19" s="68"/>
       <c r="T19" s="29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A20" s="16">
         <v>12</v>
       </c>
@@ -3895,12 +3895,12 @@
         <f t="shared" si="0"/>
         <v>157.52000000000001</v>
       </c>
-      <c r="S20" s="49"/>
+      <c r="S20" s="68"/>
       <c r="T20" s="29" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="16">
         <v>13</v>
       </c>
@@ -3947,7 +3947,7 @@
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="S21" s="49"/>
+      <c r="S21" s="68"/>
       <c r="T21" s="29" t="s">
         <v>95</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A22" s="16">
         <v>14</v>
       </c>
@@ -4002,7 +4002,7 @@
         <f t="shared" si="0"/>
         <v>187.26400000000001</v>
       </c>
-      <c r="S22" s="49"/>
+      <c r="S22" s="68"/>
       <c r="T22" s="29" t="s">
         <v>96</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A23" s="19">
         <v>15</v>
       </c>
@@ -4057,14 +4057,14 @@
         <f t="shared" si="0"/>
         <v>247.66399999999999</v>
       </c>
-      <c r="S23" s="50" t="s">
+      <c r="S23" s="69" t="s">
         <v>81</v>
       </c>
       <c r="T23" s="30" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A24" s="19">
         <v>16</v>
       </c>
@@ -4111,12 +4111,12 @@
         <f t="shared" si="0"/>
         <v>273.05599999999998</v>
       </c>
-      <c r="S24" s="51"/>
+      <c r="S24" s="70"/>
       <c r="T24" s="30" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A25" s="19">
         <v>17</v>
       </c>
@@ -4163,7 +4163,7 @@
         <f t="shared" si="0"/>
         <v>306.17599999999999</v>
       </c>
-      <c r="S25" s="51"/>
+      <c r="S25" s="70"/>
       <c r="T25" s="30" t="s">
         <v>100</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="22">
         <v>18</v>
       </c>
@@ -4218,7 +4218,7 @@
         <f t="shared" si="0"/>
         <v>611.904</v>
       </c>
-      <c r="S26" s="52" t="s">
+      <c r="S26" s="71" t="s">
         <v>82</v>
       </c>
       <c r="T26" s="31" t="s">
@@ -4228,7 +4228,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A27" s="22">
         <v>19</v>
       </c>
@@ -4275,12 +4275,12 @@
         <f t="shared" si="0"/>
         <v>703.10400000000004</v>
       </c>
-      <c r="S27" s="53"/>
+      <c r="S27" s="72"/>
       <c r="T27" s="31" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A28" s="22">
         <v>20</v>
       </c>
@@ -4327,12 +4327,12 @@
         <f t="shared" si="0"/>
         <v>812.54399999999998</v>
       </c>
-      <c r="S28" s="53"/>
+      <c r="S28" s="72"/>
       <c r="T28" s="31" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="22">
         <v>21</v>
       </c>
@@ -4379,60 +4379,60 @@
         <f t="shared" si="0"/>
         <v>971.52</v>
       </c>
-      <c r="S29" s="53"/>
+      <c r="S29" s="72"/>
       <c r="T29" s="32" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A32" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="55" t="s">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A33" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="40" t="s">
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="55" t="s">
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A34" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A35" s="54" t="s">
         <v>41</v>
       </c>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="Q35" s="54"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A36" s="54"/>
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
@@ -4510,17 +4510,17 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="54"/>
     </row>
-    <row r="37" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13">
         <v>1</v>
       </c>
-      <c r="B37" s="59">
+      <c r="B37" s="33">
         <v>0</v>
       </c>
-      <c r="C37" s="59">
+      <c r="C37" s="33">
         <v>0</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D37" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E37" s="13">
@@ -4531,7 +4531,7 @@
         <f>C37/4</f>
         <v>0</v>
       </c>
-      <c r="G37" s="60">
+      <c r="G37" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H37" s="13">
@@ -4542,7 +4542,7 @@
         <f>C37/4</f>
         <v>0</v>
       </c>
-      <c r="J37" s="60">
+      <c r="J37" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K37" s="13">
@@ -4553,7 +4553,7 @@
         <f>C37/4</f>
         <v>0</v>
       </c>
-      <c r="M37" s="60">
+      <c r="M37" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N37" s="13">
@@ -4564,23 +4564,23 @@
         <f>C37/4</f>
         <v>0</v>
       </c>
-      <c r="P37" s="57">
+      <c r="P37" s="55">
         <f>E37+H37+K37+N37</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="58"/>
-    </row>
-    <row r="38" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q37" s="56"/>
+    </row>
+    <row r="38" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13">
         <v>2</v>
       </c>
-      <c r="B38" s="59">
+      <c r="B38" s="33">
         <v>4</v>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="33">
         <v>0</v>
       </c>
-      <c r="D38" s="60">
+      <c r="D38" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E38" s="13">
@@ -4591,7 +4591,7 @@
         <f t="shared" ref="F38:F57" si="2">C38/4</f>
         <v>0</v>
       </c>
-      <c r="G38" s="60">
+      <c r="G38" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H38" s="13">
@@ -4602,7 +4602,7 @@
         <f t="shared" ref="I38:I57" si="4">C38/4</f>
         <v>0</v>
       </c>
-      <c r="J38" s="60">
+      <c r="J38" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K38" s="13">
@@ -4613,7 +4613,7 @@
         <f t="shared" ref="L38:L57" si="6">C38/4</f>
         <v>0</v>
       </c>
-      <c r="M38" s="60">
+      <c r="M38" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N38" s="13">
@@ -4624,23 +4624,23 @@
         <f t="shared" ref="O38:O57" si="8">C38/4</f>
         <v>0</v>
       </c>
-      <c r="P38" s="57">
+      <c r="P38" s="55">
         <f t="shared" ref="P38:P57" si="9">E38+H38+K38+N38</f>
         <v>6</v>
       </c>
-      <c r="Q38" s="58"/>
-    </row>
-    <row r="39" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q38" s="56"/>
+    </row>
+    <row r="39" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13">
         <v>3</v>
       </c>
-      <c r="B39" s="59">
+      <c r="B39" s="33">
         <v>8</v>
       </c>
-      <c r="C39" s="59">
+      <c r="C39" s="33">
         <v>0</v>
       </c>
-      <c r="D39" s="60">
+      <c r="D39" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E39" s="13">
@@ -4651,7 +4651,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G39" s="60">
+      <c r="G39" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H39" s="13">
@@ -4662,7 +4662,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J39" s="60">
+      <c r="J39" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K39" s="13">
@@ -4673,7 +4673,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M39" s="60">
+      <c r="M39" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N39" s="13">
@@ -4684,23 +4684,23 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P39" s="57">
+      <c r="P39" s="55">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="Q39" s="58"/>
-    </row>
-    <row r="40" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q39" s="56"/>
+    </row>
+    <row r="40" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13">
         <v>4</v>
       </c>
-      <c r="B40" s="59">
+      <c r="B40" s="33">
         <v>8</v>
       </c>
-      <c r="C40" s="59">
+      <c r="C40" s="33">
         <v>4</v>
       </c>
-      <c r="D40" s="60">
+      <c r="D40" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E40" s="13">
@@ -4711,7 +4711,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G40" s="60">
+      <c r="G40" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H40" s="13">
@@ -4722,7 +4722,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J40" s="60">
+      <c r="J40" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K40" s="13">
@@ -4733,7 +4733,7 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="M40" s="60">
+      <c r="M40" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N40" s="13">
@@ -4744,23 +4744,23 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="P40" s="57">
+      <c r="P40" s="55">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="Q40" s="58"/>
-    </row>
-    <row r="41" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q40" s="56"/>
+    </row>
+    <row r="41" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A41" s="13">
         <v>5</v>
       </c>
-      <c r="B41" s="59">
+      <c r="B41" s="33">
         <v>12</v>
       </c>
-      <c r="C41" s="59">
+      <c r="C41" s="33">
         <v>4</v>
       </c>
-      <c r="D41" s="60">
+      <c r="D41" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E41" s="13">
@@ -4771,7 +4771,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G41" s="60">
+      <c r="G41" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H41" s="13">
@@ -4782,7 +4782,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J41" s="60">
+      <c r="J41" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K41" s="13">
@@ -4793,7 +4793,7 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="M41" s="60">
+      <c r="M41" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N41" s="13">
@@ -4804,23 +4804,23 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="P41" s="57">
+      <c r="P41" s="55">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="Q41" s="58"/>
-    </row>
-    <row r="42" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q41" s="56"/>
+    </row>
+    <row r="42" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A42" s="13">
         <v>6</v>
       </c>
-      <c r="B42" s="59">
+      <c r="B42" s="33">
         <v>16</v>
       </c>
-      <c r="C42" s="59">
+      <c r="C42" s="33">
         <v>4</v>
       </c>
-      <c r="D42" s="60">
+      <c r="D42" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E42" s="13">
@@ -4831,7 +4831,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G42" s="60">
+      <c r="G42" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H42" s="13">
@@ -4842,7 +4842,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J42" s="60">
+      <c r="J42" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K42" s="13">
@@ -4853,7 +4853,7 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="M42" s="60">
+      <c r="M42" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N42" s="13">
@@ -4864,23 +4864,23 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="P42" s="57">
+      <c r="P42" s="55">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q42" s="58"/>
-    </row>
-    <row r="43" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q42" s="56"/>
+    </row>
+    <row r="43" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13">
         <v>7</v>
       </c>
-      <c r="B43" s="59">
+      <c r="B43" s="33">
         <v>16</v>
       </c>
-      <c r="C43" s="59">
+      <c r="C43" s="33">
         <v>8</v>
       </c>
-      <c r="D43" s="60">
+      <c r="D43" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E43" s="13">
@@ -4891,7 +4891,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G43" s="60">
+      <c r="G43" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H43" s="13">
@@ -4902,7 +4902,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J43" s="60">
+      <c r="J43" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K43" s="13">
@@ -4913,7 +4913,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="M43" s="60">
+      <c r="M43" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N43" s="13">
@@ -4924,23 +4924,23 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="P43" s="57">
+      <c r="P43" s="55">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q43" s="58"/>
-    </row>
-    <row r="44" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q43" s="56"/>
+    </row>
+    <row r="44" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A44" s="13">
         <v>8</v>
       </c>
-      <c r="B44" s="59">
+      <c r="B44" s="33">
         <v>20</v>
       </c>
-      <c r="C44" s="59">
+      <c r="C44" s="33">
         <v>8</v>
       </c>
-      <c r="D44" s="60">
+      <c r="D44" s="34">
         <v>0.20799999999999999</v>
       </c>
       <c r="E44" s="13">
@@ -4951,7 +4951,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G44" s="60">
+      <c r="G44" s="34">
         <v>0.33300000000000002</v>
       </c>
       <c r="H44" s="13">
@@ -4962,7 +4962,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J44" s="60">
+      <c r="J44" s="34">
         <v>0.29099999999999998</v>
       </c>
       <c r="K44" s="13">
@@ -4973,7 +4973,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="M44" s="60">
+      <c r="M44" s="34">
         <v>0.16600000000000001</v>
       </c>
       <c r="N44" s="13">
@@ -4984,23 +4984,23 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="P44" s="57">
+      <c r="P44" s="55">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q44" s="58"/>
-    </row>
-    <row r="45" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q44" s="56"/>
+    </row>
+    <row r="45" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A45" s="16">
         <v>9</v>
       </c>
-      <c r="B45" s="61">
+      <c r="B45" s="35">
         <v>24</v>
       </c>
-      <c r="C45" s="61">
+      <c r="C45" s="35">
         <v>8</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="36">
         <v>0.20799999999999999</v>
       </c>
       <c r="E45" s="16">
@@ -5011,7 +5011,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G45" s="62">
+      <c r="G45" s="36">
         <v>0.33300000000000002</v>
       </c>
       <c r="H45" s="16">
@@ -5022,7 +5022,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J45" s="62">
+      <c r="J45" s="36">
         <v>0.29099999999999998</v>
       </c>
       <c r="K45" s="16">
@@ -5033,7 +5033,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="M45" s="62">
+      <c r="M45" s="36">
         <v>0.16600000000000001</v>
       </c>
       <c r="N45" s="16">
@@ -5044,23 +5044,23 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="P45" s="63">
+      <c r="P45" s="57">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="Q45" s="64"/>
-    </row>
-    <row r="46" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q45" s="58"/>
+    </row>
+    <row r="46" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A46" s="16">
         <v>10</v>
       </c>
-      <c r="B46" s="61">
+      <c r="B46" s="35">
         <v>28</v>
       </c>
-      <c r="C46" s="61">
+      <c r="C46" s="35">
         <v>12</v>
       </c>
-      <c r="D46" s="62">
+      <c r="D46" s="36">
         <v>0.20799999999999999</v>
       </c>
       <c r="E46" s="16">
@@ -5071,7 +5071,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="G46" s="62">
+      <c r="G46" s="36">
         <v>0.33300000000000002</v>
       </c>
       <c r="H46" s="16">
@@ -5082,7 +5082,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J46" s="62">
+      <c r="J46" s="36">
         <v>0.29099999999999998</v>
       </c>
       <c r="K46" s="16">
@@ -5093,7 +5093,7 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="M46" s="62">
+      <c r="M46" s="36">
         <v>0.16600000000000001</v>
       </c>
       <c r="N46" s="16">
@@ -5104,23 +5104,23 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="P46" s="63">
+      <c r="P46" s="57">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="Q46" s="64"/>
-    </row>
-    <row r="47" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q46" s="58"/>
+    </row>
+    <row r="47" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A47" s="16">
         <v>11</v>
       </c>
-      <c r="B47" s="61">
+      <c r="B47" s="35">
         <v>32</v>
       </c>
-      <c r="C47" s="61">
+      <c r="C47" s="35">
         <v>12</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="36">
         <v>0.20799999999999999</v>
       </c>
       <c r="E47" s="16">
@@ -5131,7 +5131,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="G47" s="62">
+      <c r="G47" s="36">
         <v>0.33300000000000002</v>
       </c>
       <c r="H47" s="16">
@@ -5142,7 +5142,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J47" s="62">
+      <c r="J47" s="36">
         <v>0.29099999999999998</v>
       </c>
       <c r="K47" s="16">
@@ -5153,7 +5153,7 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="M47" s="62">
+      <c r="M47" s="36">
         <v>0.16600000000000001</v>
       </c>
       <c r="N47" s="16">
@@ -5164,23 +5164,23 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="P47" s="63">
+      <c r="P47" s="57">
         <f t="shared" si="9"/>
         <v>34</v>
       </c>
-      <c r="Q47" s="64"/>
-    </row>
-    <row r="48" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q47" s="58"/>
+    </row>
+    <row r="48" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A48" s="16">
         <v>12</v>
       </c>
-      <c r="B48" s="61">
+      <c r="B48" s="35">
         <v>36</v>
       </c>
-      <c r="C48" s="61">
+      <c r="C48" s="35">
         <v>12</v>
       </c>
-      <c r="D48" s="62">
+      <c r="D48" s="36">
         <v>0.20799999999999999</v>
       </c>
       <c r="E48" s="16">
@@ -5191,7 +5191,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="G48" s="62">
+      <c r="G48" s="36">
         <v>0.33300000000000002</v>
       </c>
       <c r="H48" s="16">
@@ -5202,7 +5202,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J48" s="62">
+      <c r="J48" s="36">
         <v>0.29099999999999998</v>
       </c>
       <c r="K48" s="16">
@@ -5213,7 +5213,7 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="M48" s="62">
+      <c r="M48" s="36">
         <v>0.16600000000000001</v>
       </c>
       <c r="N48" s="16">
@@ -5224,23 +5224,23 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="P48" s="63">
+      <c r="P48" s="57">
         <f t="shared" si="9"/>
         <v>37</v>
       </c>
-      <c r="Q48" s="64"/>
-    </row>
-    <row r="49" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q48" s="58"/>
+    </row>
+    <row r="49" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A49" s="16">
         <v>13</v>
       </c>
-      <c r="B49" s="61">
+      <c r="B49" s="35">
         <v>40</v>
       </c>
-      <c r="C49" s="61">
+      <c r="C49" s="35">
         <v>12</v>
       </c>
-      <c r="D49" s="62">
+      <c r="D49" s="36">
         <v>0.20799999999999999</v>
       </c>
       <c r="E49" s="16">
@@ -5251,7 +5251,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="G49" s="62">
+      <c r="G49" s="36">
         <v>0.33300000000000002</v>
       </c>
       <c r="H49" s="16">
@@ -5262,7 +5262,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J49" s="62">
+      <c r="J49" s="36">
         <v>0.29099999999999998</v>
       </c>
       <c r="K49" s="16">
@@ -5273,7 +5273,7 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="M49" s="62">
+      <c r="M49" s="36">
         <v>0.16600000000000001</v>
       </c>
       <c r="N49" s="16">
@@ -5284,23 +5284,23 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="P49" s="63">
+      <c r="P49" s="57">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="Q49" s="64"/>
-    </row>
-    <row r="50" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q49" s="58"/>
+    </row>
+    <row r="50" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A50" s="16">
         <v>14</v>
       </c>
-      <c r="B50" s="61">
+      <c r="B50" s="35">
         <v>40</v>
       </c>
-      <c r="C50" s="61">
+      <c r="C50" s="35">
         <v>16</v>
       </c>
-      <c r="D50" s="62">
+      <c r="D50" s="36">
         <v>0.20799999999999999</v>
       </c>
       <c r="E50" s="16">
@@ -5311,7 +5311,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G50" s="62">
+      <c r="G50" s="36">
         <v>0.33300000000000002</v>
       </c>
       <c r="H50" s="16">
@@ -5322,7 +5322,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="J50" s="62">
+      <c r="J50" s="36">
         <v>0.29099999999999998</v>
       </c>
       <c r="K50" s="16">
@@ -5333,7 +5333,7 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="M50" s="62">
+      <c r="M50" s="36">
         <v>0.16600000000000001</v>
       </c>
       <c r="N50" s="16">
@@ -5344,23 +5344,23 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="P50" s="63">
+      <c r="P50" s="57">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="Q50" s="64"/>
-    </row>
-    <row r="51" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q50" s="58"/>
+    </row>
+    <row r="51" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A51" s="19">
         <v>15</v>
       </c>
-      <c r="B51" s="65">
+      <c r="B51" s="37">
         <v>44</v>
       </c>
-      <c r="C51" s="65">
+      <c r="C51" s="37">
         <v>16</v>
       </c>
-      <c r="D51" s="66">
+      <c r="D51" s="38">
         <v>0.20799999999999999</v>
       </c>
       <c r="E51" s="19">
@@ -5371,7 +5371,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G51" s="66">
+      <c r="G51" s="38">
         <v>0.33300000000000002</v>
       </c>
       <c r="H51" s="19">
@@ -5382,7 +5382,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="J51" s="66">
+      <c r="J51" s="38">
         <v>0.29099999999999998</v>
       </c>
       <c r="K51" s="19">
@@ -5393,7 +5393,7 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="M51" s="66">
+      <c r="M51" s="38">
         <v>0.16600000000000001</v>
       </c>
       <c r="N51" s="19">
@@ -5404,23 +5404,23 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="P51" s="67">
+      <c r="P51" s="59">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
-      <c r="Q51" s="68"/>
-    </row>
-    <row r="52" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q51" s="60"/>
+    </row>
+    <row r="52" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A52" s="19">
         <v>16</v>
       </c>
-      <c r="B52" s="65">
+      <c r="B52" s="37">
         <v>52</v>
       </c>
-      <c r="C52" s="65">
+      <c r="C52" s="37">
         <v>20</v>
       </c>
-      <c r="D52" s="66">
+      <c r="D52" s="38">
         <v>0.20799999999999999</v>
       </c>
       <c r="E52" s="19">
@@ -5431,7 +5431,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="G52" s="66">
+      <c r="G52" s="38">
         <v>0.33300000000000002</v>
       </c>
       <c r="H52" s="19">
@@ -5442,7 +5442,7 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="J52" s="66">
+      <c r="J52" s="38">
         <v>0.29099999999999998</v>
       </c>
       <c r="K52" s="19">
@@ -5453,7 +5453,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="M52" s="66">
+      <c r="M52" s="38">
         <v>0.16600000000000001</v>
       </c>
       <c r="N52" s="19">
@@ -5464,23 +5464,23 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="P52" s="67">
+      <c r="P52" s="59">
         <f t="shared" si="9"/>
         <v>54</v>
       </c>
-      <c r="Q52" s="68"/>
-    </row>
-    <row r="53" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q52" s="60"/>
+    </row>
+    <row r="53" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A53" s="19">
         <v>17</v>
       </c>
-      <c r="B53" s="65">
+      <c r="B53" s="37">
         <v>56</v>
       </c>
-      <c r="C53" s="65">
+      <c r="C53" s="37">
         <v>24</v>
       </c>
-      <c r="D53" s="66">
+      <c r="D53" s="38">
         <v>0.20799999999999999</v>
       </c>
       <c r="E53" s="19">
@@ -5491,7 +5491,7 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="G53" s="66">
+      <c r="G53" s="38">
         <v>0.33300000000000002</v>
       </c>
       <c r="H53" s="19">
@@ -5502,7 +5502,7 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="J53" s="66">
+      <c r="J53" s="38">
         <v>0.29099999999999998</v>
       </c>
       <c r="K53" s="19">
@@ -5513,7 +5513,7 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="M53" s="66">
+      <c r="M53" s="38">
         <v>0.16600000000000001</v>
       </c>
       <c r="N53" s="19">
@@ -5524,23 +5524,23 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="P53" s="67">
+      <c r="P53" s="59">
         <f t="shared" si="9"/>
         <v>58</v>
       </c>
-      <c r="Q53" s="68"/>
-    </row>
-    <row r="54" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q53" s="60"/>
+    </row>
+    <row r="54" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A54" s="22">
         <v>18</v>
       </c>
-      <c r="B54" s="69">
+      <c r="B54" s="39">
         <v>60</v>
       </c>
-      <c r="C54" s="69">
+      <c r="C54" s="39">
         <v>28</v>
       </c>
-      <c r="D54" s="70">
+      <c r="D54" s="40">
         <v>0.20799999999999999</v>
       </c>
       <c r="E54" s="22">
@@ -5551,7 +5551,7 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="G54" s="70">
+      <c r="G54" s="40">
         <v>0.33300000000000002</v>
       </c>
       <c r="H54" s="22">
@@ -5562,7 +5562,7 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="J54" s="70">
+      <c r="J54" s="40">
         <v>0.29099999999999998</v>
       </c>
       <c r="K54" s="22">
@@ -5573,7 +5573,7 @@
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="M54" s="70">
+      <c r="M54" s="40">
         <v>0.16600000000000001</v>
       </c>
       <c r="N54" s="22">
@@ -5584,23 +5584,23 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="P54" s="71">
+      <c r="P54" s="61">
         <f t="shared" si="9"/>
         <v>61</v>
       </c>
-      <c r="Q54" s="72"/>
-    </row>
-    <row r="55" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q54" s="62"/>
+    </row>
+    <row r="55" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A55" s="22">
         <v>19</v>
       </c>
-      <c r="B55" s="69">
+      <c r="B55" s="39">
         <v>64</v>
       </c>
-      <c r="C55" s="69">
+      <c r="C55" s="39">
         <v>32</v>
       </c>
-      <c r="D55" s="70">
+      <c r="D55" s="40">
         <v>0.20799999999999999</v>
       </c>
       <c r="E55" s="22">
@@ -5611,7 +5611,7 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="G55" s="70">
+      <c r="G55" s="40">
         <v>0.33300000000000002</v>
       </c>
       <c r="H55" s="22">
@@ -5622,7 +5622,7 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="J55" s="70">
+      <c r="J55" s="40">
         <v>0.29099999999999998</v>
       </c>
       <c r="K55" s="22">
@@ -5633,7 +5633,7 @@
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="M55" s="70">
+      <c r="M55" s="40">
         <v>0.16600000000000001</v>
       </c>
       <c r="N55" s="22">
@@ -5644,23 +5644,23 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="P55" s="71">
+      <c r="P55" s="61">
         <f t="shared" si="9"/>
         <v>66</v>
       </c>
-      <c r="Q55" s="72"/>
-    </row>
-    <row r="56" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q55" s="62"/>
+    </row>
+    <row r="56" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A56" s="22">
         <v>20</v>
       </c>
-      <c r="B56" s="69">
+      <c r="B56" s="39">
         <v>68</v>
       </c>
-      <c r="C56" s="69">
+      <c r="C56" s="39">
         <v>36</v>
       </c>
-      <c r="D56" s="70">
+      <c r="D56" s="40">
         <v>0.20799999999999999</v>
       </c>
       <c r="E56" s="22">
@@ -5671,7 +5671,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="G56" s="70">
+      <c r="G56" s="40">
         <v>0.33300000000000002</v>
       </c>
       <c r="H56" s="22">
@@ -5682,7 +5682,7 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="J56" s="70">
+      <c r="J56" s="40">
         <v>0.29099999999999998</v>
       </c>
       <c r="K56" s="22">
@@ -5693,7 +5693,7 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="M56" s="70">
+      <c r="M56" s="40">
         <v>0.16600000000000001</v>
       </c>
       <c r="N56" s="22">
@@ -5704,23 +5704,23 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="P56" s="71">
+      <c r="P56" s="61">
         <f t="shared" si="9"/>
         <v>70</v>
       </c>
-      <c r="Q56" s="72"/>
-    </row>
-    <row r="57" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q56" s="62"/>
+    </row>
+    <row r="57" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A57" s="22">
         <v>21</v>
       </c>
-      <c r="B57" s="69">
+      <c r="B57" s="39">
         <v>72</v>
       </c>
-      <c r="C57" s="69">
+      <c r="C57" s="39">
         <v>40</v>
       </c>
-      <c r="D57" s="70">
+      <c r="D57" s="40">
         <v>0.20799999999999999</v>
       </c>
       <c r="E57" s="22">
@@ -5731,7 +5731,7 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="G57" s="70">
+      <c r="G57" s="40">
         <v>0.33300000000000002</v>
       </c>
       <c r="H57" s="22">
@@ -5742,7 +5742,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="J57" s="70">
+      <c r="J57" s="40">
         <v>0.29099999999999998</v>
       </c>
       <c r="K57" s="22">
@@ -5753,7 +5753,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="M57" s="70">
+      <c r="M57" s="40">
         <v>0.16600000000000001</v>
       </c>
       <c r="N57" s="22">
@@ -5764,43 +5764,43 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="P57" s="71">
+      <c r="P57" s="61">
         <f t="shared" si="9"/>
         <v>72</v>
       </c>
-      <c r="Q57" s="72"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="39" t="s">
+      <c r="Q57" s="62"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A82" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B82" s="39"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
-      <c r="L82" s="39"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="55" t="s">
+      <c r="B82" s="45"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="45"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="45"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A83" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B83" s="55"/>
-      <c r="C83" s="55"/>
-      <c r="D83" s="55"/>
-      <c r="E83" s="55"/>
-      <c r="F83" s="55"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="40" t="s">
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="52"/>
+      <c r="G83" s="52"/>
+      <c r="H83" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="I83" s="40"/>
-      <c r="J83" s="40"/>
+      <c r="I83" s="46"/>
+      <c r="J83" s="46"/>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
         <v>71</v>
       </c>
@@ -5839,15 +5839,15 @@
       <c r="J84" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K84" s="36">
+      <c r="K84" s="42">
         <v>2</v>
       </c>
-      <c r="L84" s="36">
+      <c r="L84" s="42">
         <f>I85*(H85-K84)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
         <v>42</v>
       </c>
@@ -5856,14 +5856,14 @@
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="36"/>
-      <c r="H85" s="36"/>
-      <c r="I85" s="36"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
-      <c r="L85" s="38"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="44"/>
+      <c r="K85" s="44"/>
+      <c r="L85" s="44"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
         <v>43</v>
       </c>
@@ -5872,19 +5872,19 @@
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="37"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+      <c r="G86" s="43"/>
+      <c r="H86" s="43"/>
+      <c r="I86" s="43"/>
       <c r="J86" s="54"/>
-      <c r="K86" s="36">
+      <c r="K86" s="42">
         <v>10</v>
       </c>
-      <c r="L86" s="36">
+      <c r="L86" s="42">
         <f>I85*(H85-K86)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="3" t="s">
         <v>44</v>
       </c>
@@ -5893,14 +5893,14 @@
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="G87" s="43"/>
+      <c r="H87" s="43"/>
+      <c r="I87" s="43"/>
       <c r="J87" s="54"/>
-      <c r="K87" s="38"/>
-      <c r="L87" s="38"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K87" s="44"/>
+      <c r="L87" s="44"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A88" s="3" t="s">
         <v>45</v>
       </c>
@@ -5909,19 +5909,19 @@
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="G88" s="43"/>
+      <c r="H88" s="43"/>
+      <c r="I88" s="43"/>
       <c r="J88" s="54"/>
-      <c r="K88" s="36">
+      <c r="K88" s="42">
         <v>25</v>
       </c>
-      <c r="L88" s="36">
+      <c r="L88" s="42">
         <f>I85*(H85-K88)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A89" s="3" t="s">
         <v>46</v>
       </c>
@@ -5930,14 +5930,14 @@
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-      <c r="G89" s="37"/>
-      <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
+      <c r="G89" s="43"/>
+      <c r="H89" s="43"/>
+      <c r="I89" s="43"/>
       <c r="J89" s="54"/>
-      <c r="K89" s="38"/>
-      <c r="L89" s="38"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K89" s="44"/>
+      <c r="L89" s="44"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A90" s="3" t="s">
         <v>47</v>
       </c>
@@ -5946,19 +5946,19 @@
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
+      <c r="G90" s="43"/>
+      <c r="H90" s="43"/>
+      <c r="I90" s="43"/>
       <c r="J90" s="54"/>
-      <c r="K90" s="36">
+      <c r="K90" s="42">
         <v>100</v>
       </c>
-      <c r="L90" s="36">
+      <c r="L90" s="42">
         <f>I85*(H85-K90)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A91" s="3" t="s">
         <v>48</v>
       </c>
@@ -5967,14 +5967,14 @@
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
+      <c r="G91" s="43"/>
+      <c r="H91" s="43"/>
+      <c r="I91" s="43"/>
       <c r="J91" s="54"/>
-      <c r="K91" s="38"/>
-      <c r="L91" s="38"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K91" s="44"/>
+      <c r="L91" s="44"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A92" s="3" t="s">
         <v>49</v>
       </c>
@@ -5983,19 +5983,19 @@
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
+      <c r="G92" s="43"/>
+      <c r="H92" s="43"/>
+      <c r="I92" s="43"/>
       <c r="J92" s="54"/>
-      <c r="K92" s="36">
+      <c r="K92" s="42">
         <v>200</v>
       </c>
-      <c r="L92" s="36">
+      <c r="L92" s="42">
         <f>I85*(H85-K92)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A93" s="3" t="s">
         <v>39</v>
       </c>
@@ -6004,45 +6004,34 @@
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
+      <c r="G93" s="44"/>
+      <c r="H93" s="44"/>
+      <c r="I93" s="44"/>
       <c r="J93" s="54"/>
-      <c r="K93" s="38"/>
-      <c r="L93" s="38"/>
+      <c r="K93" s="44"/>
+      <c r="L93" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:R7"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="S12:S16"/>
+    <mergeCell ref="S17:S22"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="S26:S29"/>
+    <mergeCell ref="L84:L85"/>
+    <mergeCell ref="L86:L87"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="L92:L93"/>
+    <mergeCell ref="G85:G93"/>
+    <mergeCell ref="H85:H93"/>
+    <mergeCell ref="I85:I93"/>
+    <mergeCell ref="J85:J93"/>
+    <mergeCell ref="K84:K85"/>
+    <mergeCell ref="K86:K87"/>
+    <mergeCell ref="K88:K89"/>
+    <mergeCell ref="K90:K91"/>
+    <mergeCell ref="K92:K93"/>
     <mergeCell ref="P57:Q57"/>
     <mergeCell ref="A82:L82"/>
     <mergeCell ref="A83:G83"/>
@@ -6059,25 +6048,36 @@
     <mergeCell ref="P47:Q47"/>
     <mergeCell ref="P48:Q48"/>
     <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="G85:G93"/>
-    <mergeCell ref="H85:H93"/>
-    <mergeCell ref="I85:I93"/>
-    <mergeCell ref="J85:J93"/>
-    <mergeCell ref="K84:K85"/>
-    <mergeCell ref="K86:K87"/>
-    <mergeCell ref="K88:K89"/>
-    <mergeCell ref="K90:K91"/>
-    <mergeCell ref="K92:K93"/>
-    <mergeCell ref="L84:L85"/>
-    <mergeCell ref="L86:L87"/>
-    <mergeCell ref="L88:L89"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="L92:L93"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="S12:S16"/>
-    <mergeCell ref="S17:S22"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S26:S29"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:R7"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6088,9 +6088,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>77</v>
       </c>

--- a/dev_stuffs/2玩家数值模型.xlsx
+++ b/dev_stuffs/2玩家数值模型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C222CE-9407-4DA8-B9B7-CA8675085AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0391D8BD-E7D4-4A9A-B69D-28FAFEFE6D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="4920" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="21105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="伤害计算" sheetId="1" r:id="rId1"/>
@@ -19,22 +19,11 @@
     <sheet name="角色属性构成" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="108">
   <si>
     <t>伤害计算公式</t>
   </si>
@@ -394,7 +383,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +396,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
@@ -415,6 +405,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -422,6 +413,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -433,6 +425,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -533,7 +534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -545,32 +546,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -619,6 +594,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -640,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -662,7 +646,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -677,7 +661,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
@@ -725,21 +709,6 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="3" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="4" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -764,16 +733,46 @@
     <xf numFmtId="10" fontId="3" fillId="15" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -785,16 +784,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -803,61 +793,52 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1136,20 +1117,20 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="42"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
@@ -1281,77 +1262,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="H1" s="49" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="H1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="H3" s="50" t="s">
+      <c r="B3" s="48"/>
+      <c r="H3" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="50"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="H4" s="50" t="s">
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="H4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="H5" s="45" t="s">
+      <c r="B5" s="49"/>
+      <c r="H5" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="45" t="s">
+      <c r="I5" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45" t="s">
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
@@ -1369,8 +1350,8 @@
       <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="45"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1391,7 +1372,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A7" s="42">
+      <c r="A7" s="45">
         <v>1</v>
       </c>
       <c r="B7" s="3">
@@ -1405,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="H7" s="42">
+      <c r="H7" s="45">
         <v>1</v>
       </c>
       <c r="I7" s="3">
@@ -1437,7 +1418,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A8" s="43"/>
+      <c r="A8" s="46"/>
       <c r="B8" s="3">
         <v>1</v>
       </c>
@@ -1452,7 +1433,7 @@
         <f t="shared" ref="E8:E27" si="2">D8-D7</f>
         <v>1</v>
       </c>
-      <c r="H8" s="43"/>
+      <c r="H8" s="46"/>
       <c r="I8" s="3">
         <f t="shared" ref="I8:I27" si="3">D8</f>
         <v>11</v>
@@ -1482,7 +1463,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A9" s="43"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="3">
         <v>1</v>
       </c>
@@ -1497,7 +1478,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H9" s="43"/>
+      <c r="H9" s="46"/>
       <c r="I9" s="3">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -1527,7 +1508,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A10" s="44"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="3">
         <v>2</v>
       </c>
@@ -1542,7 +1523,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H10" s="44"/>
+      <c r="H10" s="47"/>
       <c r="I10" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -1572,7 +1553,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="42">
+      <c r="A11" s="45">
         <v>2</v>
       </c>
       <c r="B11" s="3">
@@ -1589,7 +1570,7 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="45">
         <v>2</v>
       </c>
       <c r="I11" s="3">
@@ -1621,7 +1602,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A12" s="43"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="3">
         <v>4</v>
       </c>
@@ -1636,7 +1617,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H12" s="43"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="3">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -1666,7 +1647,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="43"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="3">
         <v>4</v>
       </c>
@@ -1681,7 +1662,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H13" s="43"/>
+      <c r="H13" s="46"/>
       <c r="I13" s="3">
         <f t="shared" si="3"/>
         <v>34</v>
@@ -1711,7 +1692,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="44"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="3">
         <v>4</v>
       </c>
@@ -1726,7 +1707,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H14" s="44"/>
+      <c r="H14" s="47"/>
       <c r="I14" s="3">
         <f t="shared" si="3"/>
         <v>38</v>
@@ -1756,7 +1737,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A15" s="42">
+      <c r="A15" s="45">
         <v>3</v>
       </c>
       <c r="B15" s="3">
@@ -1773,7 +1754,7 @@
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="45">
         <v>3</v>
       </c>
       <c r="I15" s="3">
@@ -1805,7 +1786,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A16" s="43"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="3">
         <v>9</v>
       </c>
@@ -1820,7 +1801,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H16" s="43"/>
+      <c r="H16" s="46"/>
       <c r="I16" s="3">
         <f t="shared" si="3"/>
         <v>91</v>
@@ -1850,7 +1831,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A17" s="43"/>
+      <c r="A17" s="46"/>
       <c r="B17" s="3">
         <v>9</v>
       </c>
@@ -1865,7 +1846,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H17" s="43"/>
+      <c r="H17" s="46"/>
       <c r="I17" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
@@ -1895,7 +1876,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A18" s="43"/>
+      <c r="A18" s="46"/>
       <c r="B18" s="3">
         <v>9</v>
       </c>
@@ -1910,7 +1891,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H18" s="43"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="3">
         <f t="shared" si="3"/>
         <v>109</v>
@@ -1940,7 +1921,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A19" s="43"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="3">
         <v>9</v>
       </c>
@@ -1955,7 +1936,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H19" s="43"/>
+      <c r="H19" s="46"/>
       <c r="I19" s="3">
         <f t="shared" si="3"/>
         <v>118</v>
@@ -1985,7 +1966,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A20" s="44"/>
+      <c r="A20" s="47"/>
       <c r="B20" s="3">
         <v>9</v>
       </c>
@@ -2000,7 +1981,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="H20" s="44"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="3">
         <f t="shared" si="3"/>
         <v>127</v>
@@ -2030,7 +2011,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A21" s="42">
+      <c r="A21" s="45">
         <v>4</v>
       </c>
       <c r="B21" s="3">
@@ -2047,7 +2028,7 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="45">
         <v>4</v>
       </c>
       <c r="I21" s="3">
@@ -2079,7 +2060,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A22" s="43"/>
+      <c r="A22" s="46"/>
       <c r="B22" s="3">
         <v>16</v>
       </c>
@@ -2094,7 +2075,7 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="H22" s="43"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="3">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -2124,7 +2105,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A23" s="44"/>
+      <c r="A23" s="47"/>
       <c r="B23" s="3">
         <v>16</v>
       </c>
@@ -2139,7 +2120,7 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="H23" s="44"/>
+      <c r="H23" s="47"/>
       <c r="I23" s="3">
         <f t="shared" si="3"/>
         <v>266</v>
@@ -2169,7 +2150,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A24" s="42">
+      <c r="A24" s="45">
         <v>5</v>
       </c>
       <c r="B24" s="3">
@@ -2186,7 +2167,7 @@
         <f t="shared" si="2"/>
         <v>254</v>
       </c>
-      <c r="H24" s="42">
+      <c r="H24" s="45">
         <v>5</v>
       </c>
       <c r="I24" s="3">
@@ -2218,7 +2199,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A25" s="43"/>
+      <c r="A25" s="46"/>
       <c r="B25" s="3">
         <v>31</v>
       </c>
@@ -2233,7 +2214,7 @@
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="H25" s="43"/>
+      <c r="H25" s="46"/>
       <c r="I25" s="3">
         <f t="shared" si="3"/>
         <v>568</v>
@@ -2263,7 +2244,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A26" s="43"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="3">
         <v>32</v>
       </c>
@@ -2278,7 +2259,7 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="H26" s="43"/>
+      <c r="H26" s="46"/>
       <c r="I26" s="3">
         <f t="shared" si="3"/>
         <v>618</v>
@@ -2308,7 +2289,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A27" s="44"/>
+      <c r="A27" s="47"/>
       <c r="B27" s="3">
         <v>35</v>
       </c>
@@ -2323,7 +2304,7 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="H27" s="44"/>
+      <c r="H27" s="47"/>
       <c r="I27" s="3">
         <f t="shared" si="3"/>
         <v>710</v>
@@ -2361,15 +2342,15 @@
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="H32" s="48" t="s">
+      <c r="H32" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
     </row>
     <row r="33" spans="1:14" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
@@ -2377,28 +2358,28 @@
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H34" s="46" t="s">
+      <c r="H34" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I34" s="46"/>
+      <c r="I34" s="51"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H35" s="46" t="s">
+      <c r="H35" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="H36" s="1" t="s">
@@ -2424,7 +2405,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H37" s="42">
+      <c r="H37" s="45">
         <v>1</v>
       </c>
       <c r="I37" s="6">
@@ -2448,7 +2429,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H38" s="43"/>
+      <c r="H38" s="46"/>
       <c r="I38" s="6">
         <v>15</v>
       </c>
@@ -2471,7 +2452,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H39" s="43"/>
+      <c r="H39" s="46"/>
       <c r="I39" s="6">
         <v>15</v>
       </c>
@@ -2494,7 +2475,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H40" s="44"/>
+      <c r="H40" s="47"/>
       <c r="I40" s="6">
         <v>15</v>
       </c>
@@ -2517,7 +2498,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H41" s="42">
+      <c r="H41" s="45">
         <v>2</v>
       </c>
       <c r="I41" s="6">
@@ -2542,7 +2523,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H42" s="43"/>
+      <c r="H42" s="46"/>
       <c r="I42" s="6">
         <v>35</v>
       </c>
@@ -2565,7 +2546,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H43" s="43"/>
+      <c r="H43" s="46"/>
       <c r="I43" s="6">
         <v>35</v>
       </c>
@@ -2588,7 +2569,7 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H44" s="44"/>
+      <c r="H44" s="47"/>
       <c r="I44" s="6">
         <v>35</v>
       </c>
@@ -2611,7 +2592,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H45" s="42">
+      <c r="H45" s="45">
         <v>3</v>
       </c>
       <c r="I45" s="6">
@@ -2636,7 +2617,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H46" s="43"/>
+      <c r="H46" s="46"/>
       <c r="I46" s="6">
         <v>80</v>
       </c>
@@ -2659,7 +2640,7 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H47" s="43"/>
+      <c r="H47" s="46"/>
       <c r="I47" s="6">
         <v>80</v>
       </c>
@@ -2682,7 +2663,7 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="H48" s="43"/>
+      <c r="H48" s="46"/>
       <c r="I48" s="6">
         <v>80</v>
       </c>
@@ -2705,7 +2686,7 @@
       </c>
     </row>
     <row r="49" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H49" s="43"/>
+      <c r="H49" s="46"/>
       <c r="I49" s="6">
         <v>80</v>
       </c>
@@ -2728,7 +2709,7 @@
       </c>
     </row>
     <row r="50" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H50" s="44"/>
+      <c r="H50" s="47"/>
       <c r="I50" s="6">
         <v>80</v>
       </c>
@@ -2751,7 +2732,7 @@
       </c>
     </row>
     <row r="51" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H51" s="42">
+      <c r="H51" s="45">
         <v>4</v>
       </c>
       <c r="I51" s="6">
@@ -2776,7 +2757,7 @@
       </c>
     </row>
     <row r="52" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H52" s="43"/>
+      <c r="H52" s="46"/>
       <c r="I52" s="6">
         <v>120</v>
       </c>
@@ -2799,7 +2780,7 @@
       </c>
     </row>
     <row r="53" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H53" s="44"/>
+      <c r="H53" s="47"/>
       <c r="I53" s="6">
         <v>120</v>
       </c>
@@ -2822,7 +2803,7 @@
       </c>
     </row>
     <row r="54" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H54" s="42">
+      <c r="H54" s="45">
         <v>5</v>
       </c>
       <c r="I54" s="6">
@@ -2847,7 +2828,7 @@
       </c>
     </row>
     <row r="55" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H55" s="43"/>
+      <c r="H55" s="46"/>
       <c r="I55" s="6">
         <v>200</v>
       </c>
@@ -2870,7 +2851,7 @@
       </c>
     </row>
     <row r="56" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H56" s="43"/>
+      <c r="H56" s="46"/>
       <c r="I56" s="6">
         <v>200</v>
       </c>
@@ -2893,7 +2874,7 @@
       </c>
     </row>
     <row r="57" spans="8:14" x14ac:dyDescent="0.15">
-      <c r="H57" s="44"/>
+      <c r="H57" s="47"/>
       <c r="I57" s="6">
         <v>200</v>
       </c>
@@ -2917,6 +2898,20 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="H45:H50"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:L35"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="H15:H20"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="H1:L2"/>
     <mergeCell ref="H32:N33"/>
@@ -2932,20 +2927,6 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="H45:H50"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:L35"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="H15:H20"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:L5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3053,62 +3034,62 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U93"/>
+  <dimension ref="A1:T93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A1" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A2" s="52" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A2" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="46" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="52" t="s">
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A3" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -3120,7 +3101,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -3144,7 +3125,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -3168,7 +3149,7 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3186,1304 +3167,1125 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A7" s="41" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="45" t="s">
+      <c r="E7" s="56"/>
+      <c r="F7" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="52" t="s">
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="46" t="s">
+      <c r="I7" s="58"/>
+      <c r="J7" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A8" s="3" t="s">
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="F8" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="G8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="H8" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="I8" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="J8" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="L8" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="M8" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="N8" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="O8" s="36" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="25">
+    <row r="9" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="25">
         <v>1</v>
       </c>
-      <c r="B9" s="25">
+      <c r="E9" s="25">
         <v>6</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G9" s="26">
         <v>1</v>
       </c>
-      <c r="G9" s="25"/>
       <c r="H9" s="26">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25">
+        <f>1+H9*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="25">
+        <f>(B5+E9)*F9*I9*E5</f>
+        <v>9.9</v>
+      </c>
+      <c r="K9" s="25">
+        <v>10</v>
+      </c>
+      <c r="L9" s="25">
+        <f>C5*G9</f>
+        <v>1.6</v>
+      </c>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25">
+        <v>2</v>
+      </c>
+      <c r="O9" s="25">
+        <f>L9*(J9-N9)</f>
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="37"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="25">
+        <v>2</v>
+      </c>
+      <c r="E10" s="25">
+        <v>7</v>
+      </c>
+      <c r="F10" s="26">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I9" s="26">
+      <c r="G10" s="26">
         <v>1</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="26">
+      <c r="H10" s="26">
         <v>0</v>
       </c>
-      <c r="L9" s="25">
-        <f>1+K9*F5</f>
+      <c r="I10" s="25">
+        <f>1+H10*F5</f>
         <v>1</v>
       </c>
-      <c r="M9" s="25">
-        <f>(B5+B9)*H9*L9*E5</f>
-        <v>9.9</v>
-      </c>
-      <c r="N9" s="25">
+      <c r="J10" s="25">
+        <f>(B5+E10)*F10*I10*E5</f>
+        <v>11</v>
+      </c>
+      <c r="K10" s="25">
+        <v>11</v>
+      </c>
+      <c r="L10" s="25">
+        <f>C5*G10</f>
+        <v>1.6</v>
+      </c>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25">
+        <v>2</v>
+      </c>
+      <c r="O10" s="25">
+        <f>L10*(J10-N10)</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="37"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="25">
+        <v>3</v>
+      </c>
+      <c r="E11" s="25">
+        <v>8</v>
+      </c>
+      <c r="F11" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G11" s="26">
+        <v>1</v>
+      </c>
+      <c r="H11" s="26">
+        <v>0</v>
+      </c>
+      <c r="I11" s="25">
+        <f>1+H11*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="25">
+        <f>(B5+E11)*F11*I11*E5</f>
+        <v>12.100000000000001</v>
+      </c>
+      <c r="K11" s="25">
+        <v>12</v>
+      </c>
+      <c r="L11" s="25">
+        <f>C5*G11</f>
+        <v>1.6</v>
+      </c>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25">
+        <v>2</v>
+      </c>
+      <c r="O11" s="25">
+        <f>L11*(J11-N11)</f>
+        <v>16.160000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="13">
+        <v>4</v>
+      </c>
+      <c r="E12" s="13">
         <v>10</v>
       </c>
-      <c r="O9" s="25">
-        <f>C5*I9</f>
+      <c r="F12" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="G12" s="14">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <f>1+H12*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="13">
+        <f>(B5+E12)*F12*I12*E5</f>
+        <v>15.6</v>
+      </c>
+      <c r="K12" s="13">
+        <v>16</v>
+      </c>
+      <c r="L12" s="13">
+        <f>C5*G12</f>
         <v>1.6</v>
       </c>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25">
+      <c r="M12" s="13"/>
+      <c r="N12" s="13">
         <v>2</v>
       </c>
-      <c r="R9" s="25">
-        <f>O9*(M9-Q9)</f>
-        <v>12.64</v>
-      </c>
-      <c r="S9" s="63" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="25">
+      <c r="O12" s="13">
+        <f>L12*(J12-N12)</f>
+        <v>21.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="38"/>
+      <c r="B13" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="13">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13">
+        <v>17</v>
+      </c>
+      <c r="F13" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="G13" s="14">
+        <v>1.05</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13">
+        <f>1+H13*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="13">
+        <f>(B5+E13)*F13*I13*E5</f>
+        <v>26</v>
+      </c>
+      <c r="K13" s="13">
+        <v>26</v>
+      </c>
+      <c r="L13" s="13">
+        <f>C5*G13</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13">
+        <v>5</v>
+      </c>
+      <c r="O13" s="13">
+        <f>L13*(J13-N13)</f>
+        <v>35.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="38"/>
+      <c r="B14" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="13">
+        <v>6</v>
+      </c>
+      <c r="E14" s="13">
+        <v>20</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1.05</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <f>1+H14*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="13">
+        <f>(B5+E14)*F14*I14*E5</f>
+        <v>29.900000000000002</v>
+      </c>
+      <c r="K14" s="13">
+        <v>30</v>
+      </c>
+      <c r="L14" s="13">
+        <f>C5*G14</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13">
+        <v>5</v>
+      </c>
+      <c r="O14" s="13">
+        <f>L14*(J14-N14)</f>
+        <v>41.832000000000008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="38"/>
+      <c r="B15" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="13">
+        <v>7</v>
+      </c>
+      <c r="E15" s="13">
+        <v>23</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1.05</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
+        <f>1+H15*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="13">
+        <f>(B5+E15)*F15*I15*E5</f>
+        <v>33.800000000000004</v>
+      </c>
+      <c r="K15" s="13">
+        <v>34</v>
+      </c>
+      <c r="L15" s="13">
+        <f>C5*G15</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13">
+        <v>5</v>
+      </c>
+      <c r="O15" s="13">
+        <f>L15*(J15-N15)</f>
+        <v>48.384000000000015</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="38"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="13">
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
+        <v>25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>1.35</v>
+      </c>
+      <c r="G16" s="14">
+        <v>1.05</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
+        <f>1+H16*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="13">
+        <f>(B5+E16)*F16*I16*E5</f>
+        <v>37.800000000000004</v>
+      </c>
+      <c r="K16" s="13">
+        <v>38</v>
+      </c>
+      <c r="L16" s="13">
+        <f>C5*G16</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13">
+        <v>5</v>
+      </c>
+      <c r="O16" s="13">
+        <f>L16*(J16-N16)</f>
+        <v>55.104000000000013</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="16">
+        <v>9</v>
+      </c>
+      <c r="E17" s="16">
+        <v>52</v>
+      </c>
+      <c r="F17" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16">
+        <f>1+H17*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="16">
+        <f>(B5+E17)*F17*I17*E5</f>
+        <v>82.5</v>
+      </c>
+      <c r="K17" s="16">
+        <v>82</v>
+      </c>
+      <c r="L17" s="16">
+        <f>C5*G17</f>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16">
+        <v>20</v>
+      </c>
+      <c r="O17" s="16">
+        <f>L17*(J17-N17)</f>
+        <v>110.00000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="39"/>
+      <c r="B18" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="16">
+        <v>10</v>
+      </c>
+      <c r="E18" s="16">
+        <v>57</v>
+      </c>
+      <c r="F18" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
+        <f>1+H18*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="16">
+        <f>(B5+E18)*F18*I18*E5</f>
+        <v>90</v>
+      </c>
+      <c r="K18" s="16">
+        <v>91</v>
+      </c>
+      <c r="L18" s="16">
+        <f>C5*G18</f>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16">
+        <v>20</v>
+      </c>
+      <c r="O18" s="16">
+        <f>L18*(J18-N18)</f>
+        <v>123.20000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="39"/>
+      <c r="B19" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="16">
+        <v>11</v>
+      </c>
+      <c r="E19" s="16">
+        <v>62</v>
+      </c>
+      <c r="F19" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16">
+        <f>1+H19*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="16">
+        <f>(B5+E19)*F19*I19*E5</f>
+        <v>97.5</v>
+      </c>
+      <c r="K19" s="16">
+        <v>100</v>
+      </c>
+      <c r="L19" s="16">
+        <f>C5*G19</f>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16">
+        <v>20</v>
+      </c>
+      <c r="O19" s="16">
+        <f>L19*(J19-N19)</f>
+        <v>136.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="39"/>
+      <c r="B20" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="16">
+        <v>12</v>
+      </c>
+      <c r="E20" s="16">
+        <v>70</v>
+      </c>
+      <c r="F20" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0</v>
+      </c>
+      <c r="I20" s="16">
+        <f>1+H20*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J20" s="16">
+        <f>(B5+E20)*F20*I20*E5</f>
+        <v>109.5</v>
+      </c>
+      <c r="K20" s="16">
+        <v>109</v>
+      </c>
+      <c r="L20" s="16">
+        <f>C5*G20</f>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16">
+        <v>20</v>
+      </c>
+      <c r="O20" s="16">
+        <f>L20*(J20-N20)</f>
+        <v>157.52000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="39"/>
+      <c r="B21" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="16">
+        <v>13</v>
+      </c>
+      <c r="E21" s="16">
+        <v>72</v>
+      </c>
+      <c r="F21" s="17">
+        <v>1.6</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H21" s="17">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
+        <f>1+H21*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J21" s="16">
+        <f>(B5+E21)*F21*I21*E5</f>
+        <v>120</v>
+      </c>
+      <c r="K21" s="16">
+        <v>118</v>
+      </c>
+      <c r="L21" s="16">
+        <f>C5*G21</f>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16">
+        <v>20</v>
+      </c>
+      <c r="O21" s="16">
+        <f>L21*(J21-N21)</f>
+        <v>176.00000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="39"/>
+      <c r="B22" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="16">
+        <v>14</v>
+      </c>
+      <c r="E22" s="16">
+        <v>76</v>
+      </c>
+      <c r="F22" s="17">
+        <v>1.6</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H22" s="17">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16">
+        <f>1+H22*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="16">
+        <f>(B5+E22)*F22*I22*E5</f>
+        <v>126.4</v>
+      </c>
+      <c r="K22" s="16">
+        <v>127</v>
+      </c>
+      <c r="L22" s="16">
+        <f>C5*G22</f>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16">
+        <v>20</v>
+      </c>
+      <c r="O22" s="16">
+        <f>L22*(J22-N22)</f>
+        <v>187.26400000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="19">
+        <v>15</v>
+      </c>
+      <c r="E23" s="19">
+        <v>135</v>
+      </c>
+      <c r="F23" s="20">
+        <v>1.7</v>
+      </c>
+      <c r="G23" s="20">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H23" s="20">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19">
+        <f>1+H23*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="19">
+        <f>(B5+E23)*F23*I23*E5</f>
+        <v>234.6</v>
+      </c>
+      <c r="K23" s="19">
+        <v>234</v>
+      </c>
+      <c r="L23" s="19">
+        <f>C5*G23</f>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19">
+        <v>100</v>
+      </c>
+      <c r="O23" s="19">
+        <f>L23*(J23-N23)</f>
+        <v>247.66399999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="40"/>
+      <c r="B24" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="32"/>
+      <c r="D24" s="19">
+        <v>16</v>
+      </c>
+      <c r="E24" s="19">
+        <v>135</v>
+      </c>
+      <c r="F24" s="20">
+        <v>1.8</v>
+      </c>
+      <c r="G24" s="20">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H24" s="20">
+        <v>0</v>
+      </c>
+      <c r="I24" s="19">
+        <f>1+H24*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J24" s="19">
+        <f>(B5+E24)*F24*I24*E5</f>
+        <v>248.4</v>
+      </c>
+      <c r="K24" s="19">
+        <v>250</v>
+      </c>
+      <c r="L24" s="19">
+        <f>C5*G24</f>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19">
+        <v>100</v>
+      </c>
+      <c r="O24" s="19">
+        <f>L24*(J24-N24)</f>
+        <v>273.05599999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="40"/>
+      <c r="B25" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="19">
+        <v>17</v>
+      </c>
+      <c r="E25" s="19">
+        <v>145</v>
+      </c>
+      <c r="F25" s="20">
+        <v>1.8</v>
+      </c>
+      <c r="G25" s="20">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H25" s="20">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19">
+        <f>1+H25*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J25" s="19">
+        <f>(B5+E25)*F25*I25*E5</f>
+        <v>266.40000000000003</v>
+      </c>
+      <c r="K25" s="19">
+        <v>266</v>
+      </c>
+      <c r="L25" s="19">
+        <f>C5*G25</f>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19">
+        <v>100</v>
+      </c>
+      <c r="O25" s="19">
+        <f>L25*(J25-N25)</f>
+        <v>306.17600000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="22">
+        <v>18</v>
+      </c>
+      <c r="E26" s="22">
+        <v>270</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1.9</v>
+      </c>
+      <c r="G26" s="23">
+        <v>1.2</v>
+      </c>
+      <c r="H26" s="23">
+        <v>0</v>
+      </c>
+      <c r="I26" s="22">
+        <f>1+H26*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="22">
+        <f>(B5+E26)*F26*I26*E5</f>
+        <v>518.69999999999993</v>
+      </c>
+      <c r="K26" s="22">
+        <v>520</v>
+      </c>
+      <c r="L26" s="22">
+        <f>C5*G26</f>
+        <v>1.92</v>
+      </c>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22">
+        <v>200</v>
+      </c>
+      <c r="O26" s="22">
+        <f>L26*(J26-N26)</f>
+        <v>611.90399999999988</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="41"/>
+      <c r="B27" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="34"/>
+      <c r="D27" s="22">
+        <v>19</v>
+      </c>
+      <c r="E27" s="22">
+        <v>295</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1.9</v>
+      </c>
+      <c r="G27" s="23">
+        <v>1.2</v>
+      </c>
+      <c r="H27" s="23">
+        <v>0</v>
+      </c>
+      <c r="I27" s="22">
+        <f>1+H27*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="22">
+        <f>(B5+E27)*F27*I27*E5</f>
+        <v>566.19999999999993</v>
+      </c>
+      <c r="K27" s="22">
+        <v>568</v>
+      </c>
+      <c r="L27" s="22">
+        <f>C5*G27</f>
+        <v>1.92</v>
+      </c>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22">
+        <v>200</v>
+      </c>
+      <c r="O27" s="22">
+        <f>L27*(J27-N27)</f>
+        <v>703.10399999999981</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="41"/>
+      <c r="B28" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="34"/>
+      <c r="D28" s="22">
+        <v>20</v>
+      </c>
+      <c r="E28" s="22">
+        <v>325</v>
+      </c>
+      <c r="F28" s="23">
+        <v>1.9</v>
+      </c>
+      <c r="G28" s="23">
+        <v>1.2</v>
+      </c>
+      <c r="H28" s="23">
+        <v>0</v>
+      </c>
+      <c r="I28" s="22">
+        <f>1+H28*F5</f>
+        <v>1</v>
+      </c>
+      <c r="J28" s="22">
+        <f>(B5+E28)*F28*I28*E5</f>
+        <v>623.19999999999993</v>
+      </c>
+      <c r="K28" s="22">
+        <v>618</v>
+      </c>
+      <c r="L28" s="22">
+        <f>C5*G28</f>
+        <v>1.92</v>
+      </c>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22">
+        <v>200</v>
+      </c>
+      <c r="O28" s="22">
+        <f>L28*(J28-N28)</f>
+        <v>812.54399999999987</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="41"/>
+      <c r="B29" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="34"/>
+      <c r="D29" s="22">
+        <v>21</v>
+      </c>
+      <c r="E29" s="22">
+        <v>350</v>
+      </c>
+      <c r="F29" s="23">
         <v>2</v>
       </c>
-      <c r="B10" s="25">
-        <v>7</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25">
-        <v>2</v>
-      </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I10" s="26">
+      <c r="G29" s="23">
+        <v>1.2</v>
+      </c>
+      <c r="H29" s="23">
+        <v>0</v>
+      </c>
+      <c r="I29" s="22">
+        <f>1+H29*F5</f>
         <v>1</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26">
-        <v>0</v>
-      </c>
-      <c r="L10" s="25">
-        <f>1+K10*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="25">
-        <f>(B5+B10)*H10*L10*E5</f>
-        <v>11</v>
-      </c>
-      <c r="N10" s="25">
-        <v>11</v>
-      </c>
-      <c r="O10" s="25">
-        <f>C5*I10</f>
-        <v>1.6</v>
-      </c>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25">
-        <v>2</v>
-      </c>
-      <c r="R10" s="25">
-        <f t="shared" ref="R10:R29" si="0">O10*(M10-Q10)</f>
-        <v>14.4</v>
-      </c>
-      <c r="S10" s="64"/>
-    </row>
-    <row r="11" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="25">
-        <v>3</v>
-      </c>
-      <c r="B11" s="25">
-        <v>8</v>
-      </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25">
-        <v>3</v>
-      </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="26">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I11" s="26">
-        <v>1</v>
-      </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26">
-        <v>0</v>
-      </c>
-      <c r="L11" s="25">
-        <f>1+K11*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M11" s="25">
-        <f>(B5+B11)*H11*L11*E5</f>
-        <v>12.1</v>
-      </c>
-      <c r="N11" s="25">
-        <v>12</v>
-      </c>
-      <c r="O11" s="25">
-        <f>C5*I11</f>
-        <v>1.6</v>
-      </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25">
-        <v>2</v>
-      </c>
-      <c r="R11" s="25">
-        <f t="shared" si="0"/>
-        <v>16.16</v>
-      </c>
-      <c r="S11" s="64"/>
-    </row>
-    <row r="12" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="13">
-        <v>4</v>
-      </c>
-      <c r="B12" s="13">
-        <v>10</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13">
-        <v>4</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="I12" s="14">
-        <v>1</v>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <f>1+K12*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M12" s="13">
-        <f>(B5+B12)*H12*L12*E5</f>
-        <v>15.6</v>
-      </c>
-      <c r="N12" s="13">
-        <v>16</v>
-      </c>
-      <c r="O12" s="13">
-        <f>C5*I12</f>
-        <v>1.6</v>
-      </c>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13">
-        <v>2</v>
-      </c>
-      <c r="R12" s="13">
-        <f t="shared" si="0"/>
-        <v>21.76</v>
-      </c>
-      <c r="S12" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="T12" s="28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="13">
-        <v>5</v>
-      </c>
-      <c r="B13" s="13">
-        <v>17</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13">
-        <v>5</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="I13" s="14">
-        <v>1.05</v>
-      </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <f>1+K13*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M13" s="13">
-        <f>(B5+B13)*H13*L13*E5</f>
-        <v>26</v>
-      </c>
-      <c r="N13" s="13">
-        <v>26</v>
-      </c>
-      <c r="O13" s="13">
-        <f>C5*I13</f>
-        <v>1.68</v>
-      </c>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13">
-        <v>5</v>
-      </c>
-      <c r="R13" s="13">
-        <f t="shared" si="0"/>
-        <v>35.28</v>
-      </c>
-      <c r="S13" s="66"/>
-      <c r="T13" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="U13" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="13">
-        <v>6</v>
-      </c>
-      <c r="B14" s="13">
-        <v>20</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13">
-        <v>6</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="I14" s="14">
-        <v>1.05</v>
-      </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <f>1+K14*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M14" s="13">
-        <f>(B5+B14)*H14*L14*E5</f>
-        <v>29.9</v>
-      </c>
-      <c r="N14" s="13">
-        <v>30</v>
-      </c>
-      <c r="O14" s="13">
-        <f>C5*I14</f>
-        <v>1.68</v>
-      </c>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13">
-        <v>5</v>
-      </c>
-      <c r="R14" s="13">
-        <f t="shared" si="0"/>
-        <v>41.832000000000001</v>
-      </c>
-      <c r="S14" s="66"/>
-      <c r="T14" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="U14" s="28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="13">
-        <v>7</v>
-      </c>
-      <c r="B15" s="13">
-        <v>23</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13">
-        <v>7</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="I15" s="14">
-        <v>1.05</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <f>1+K15*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="13">
-        <f>(B5+B15)*H15*L15*E5</f>
-        <v>33.799999999999997</v>
-      </c>
-      <c r="N15" s="13">
-        <v>34</v>
-      </c>
-      <c r="O15" s="13">
-        <f>C5*I15</f>
-        <v>1.68</v>
-      </c>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13">
-        <v>5</v>
-      </c>
-      <c r="R15" s="13">
-        <f t="shared" si="0"/>
-        <v>48.384</v>
-      </c>
-      <c r="S15" s="66"/>
-      <c r="T15" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="U15" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="13">
-        <v>8</v>
-      </c>
-      <c r="B16" s="13">
-        <v>25</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13">
-        <v>8</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14">
-        <v>1.35</v>
-      </c>
-      <c r="I16" s="14">
-        <v>1.05</v>
-      </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <f>1+K16*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M16" s="13">
-        <f>(B5+B16)*H16*L16*E5</f>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="N16" s="13">
-        <v>38</v>
-      </c>
-      <c r="O16" s="13">
-        <f>C5*I16</f>
-        <v>1.68</v>
-      </c>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13">
-        <v>5</v>
-      </c>
-      <c r="R16" s="13">
-        <f t="shared" si="0"/>
-        <v>55.103999999999999</v>
-      </c>
-      <c r="S16" s="66"/>
-      <c r="U16" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="16">
-        <v>9</v>
-      </c>
-      <c r="B17" s="16">
-        <v>52</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16">
-        <v>9</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="I17" s="17">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="16">
-        <f>1+K17*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M17" s="16">
-        <f>(B5+B17)*H17*L17*E5</f>
-        <v>82.5</v>
-      </c>
-      <c r="N17" s="16">
-        <v>82</v>
-      </c>
-      <c r="O17" s="16">
-        <f>C5*I17</f>
-        <v>1.76</v>
-      </c>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16">
-        <v>20</v>
-      </c>
-      <c r="R17" s="16">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="S17" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="T17" s="29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="16">
-        <v>10</v>
-      </c>
-      <c r="B18" s="16">
+      <c r="J29" s="22">
+        <f>(B5+E29)*F29*I29*E5</f>
+        <v>706</v>
+      </c>
+      <c r="K29" s="22">
+        <v>710</v>
+      </c>
+      <c r="L29" s="22">
+        <f>C5*G29</f>
+        <v>1.92</v>
+      </c>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22">
+        <v>200</v>
+      </c>
+      <c r="O29" s="22">
+        <f>L29*(J29-N29)</f>
+        <v>971.52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A32" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A33" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16">
-        <v>10</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="I18" s="17">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17">
-        <v>0</v>
-      </c>
-      <c r="L18" s="16">
-        <f>1+K18*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M18" s="16">
-        <f>(B5+B18)*H18*L18*E5</f>
-        <v>90</v>
-      </c>
-      <c r="N18" s="16">
-        <v>91</v>
-      </c>
-      <c r="O18" s="16">
-        <f>C5*I18</f>
-        <v>1.76</v>
-      </c>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16">
-        <v>20</v>
-      </c>
-      <c r="R18" s="16">
-        <f t="shared" si="0"/>
-        <v>123.2</v>
-      </c>
-      <c r="S18" s="68"/>
-      <c r="T18" s="29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="16">
-        <v>11</v>
-      </c>
-      <c r="B19" s="16">
-        <v>62</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16">
-        <v>11</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="I19" s="17">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17">
-        <v>0</v>
-      </c>
-      <c r="L19" s="16">
-        <f>1+K19*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M19" s="16">
-        <f>(B5+B19)*H19*L19*E5</f>
-        <v>97.5</v>
-      </c>
-      <c r="N19" s="16">
-        <v>100</v>
-      </c>
-      <c r="O19" s="16">
-        <f>C5*I19</f>
-        <v>1.76</v>
-      </c>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16">
-        <v>20</v>
-      </c>
-      <c r="R19" s="16">
-        <f t="shared" si="0"/>
-        <v>136.4</v>
-      </c>
-      <c r="S19" s="68"/>
-      <c r="T19" s="29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="16">
-        <v>12</v>
-      </c>
-      <c r="B20" s="16">
-        <v>70</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16">
-        <v>12</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="I20" s="17">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="17">
-        <v>0</v>
-      </c>
-      <c r="L20" s="16">
-        <f>1+K20*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M20" s="16">
-        <f>(B5+B20)*H20*L20*E5</f>
-        <v>109.5</v>
-      </c>
-      <c r="N20" s="16">
-        <v>109</v>
-      </c>
-      <c r="O20" s="16">
-        <f>C5*I20</f>
-        <v>1.76</v>
-      </c>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16">
-        <v>20</v>
-      </c>
-      <c r="R20" s="16">
-        <f t="shared" si="0"/>
-        <v>157.52000000000001</v>
-      </c>
-      <c r="S20" s="68"/>
-      <c r="T20" s="29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="16">
-        <v>13</v>
-      </c>
-      <c r="B21" s="16">
-        <v>72</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16">
-        <v>13</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17">
-        <v>1.6</v>
-      </c>
-      <c r="I21" s="17">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="17">
-        <v>0</v>
-      </c>
-      <c r="L21" s="16">
-        <f>1+K21*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M21" s="16">
-        <f>(B5+B21)*H21*L21*E5</f>
-        <v>120</v>
-      </c>
-      <c r="N21" s="16">
-        <v>118</v>
-      </c>
-      <c r="O21" s="16">
-        <f>C5*I21</f>
-        <v>1.76</v>
-      </c>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16">
-        <v>20</v>
-      </c>
-      <c r="R21" s="16">
-        <f t="shared" si="0"/>
-        <v>176</v>
-      </c>
-      <c r="S21" s="68"/>
-      <c r="T21" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="U21" s="18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="16">
-        <v>14</v>
-      </c>
-      <c r="B22" s="16">
-        <v>76</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16">
-        <v>14</v>
-      </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="17">
-        <v>1.6</v>
-      </c>
-      <c r="I22" s="17">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J22" s="16"/>
-      <c r="K22" s="17">
-        <v>0</v>
-      </c>
-      <c r="L22" s="16">
-        <f>1+K22*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M22" s="16">
-        <f>(B5+B22)*H22*L22*E5</f>
-        <v>126.4</v>
-      </c>
-      <c r="N22" s="16">
-        <v>127</v>
-      </c>
-      <c r="O22" s="16">
-        <f>C5*I22</f>
-        <v>1.76</v>
-      </c>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16">
-        <v>20</v>
-      </c>
-      <c r="R22" s="16">
-        <f t="shared" si="0"/>
-        <v>187.26400000000001</v>
-      </c>
-      <c r="S22" s="68"/>
-      <c r="T22" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="U22" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="19">
-        <v>15</v>
-      </c>
-      <c r="B23" s="19">
-        <v>135</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19">
-        <v>15</v>
-      </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20">
-        <v>1.7</v>
-      </c>
-      <c r="I23" s="20">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="20">
-        <v>0</v>
-      </c>
-      <c r="L23" s="19">
-        <f>1+K23*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M23" s="19">
-        <f>(B5+B23)*H23*L23*E5</f>
-        <v>234.6</v>
-      </c>
-      <c r="N23" s="19">
-        <v>234</v>
-      </c>
-      <c r="O23" s="19">
-        <f>C5*I23</f>
-        <v>1.84</v>
-      </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19">
-        <v>100</v>
-      </c>
-      <c r="R23" s="19">
-        <f t="shared" si="0"/>
-        <v>247.66399999999999</v>
-      </c>
-      <c r="S23" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="T23" s="30" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="19">
-        <v>16</v>
-      </c>
-      <c r="B24" s="19">
-        <v>135</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19">
-        <v>16</v>
-      </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20">
-        <v>1.8</v>
-      </c>
-      <c r="I24" s="20">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="20">
-        <v>0</v>
-      </c>
-      <c r="L24" s="19">
-        <f>1+K24*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M24" s="19">
-        <f>(B5+B24)*H24*L24*E5</f>
-        <v>248.4</v>
-      </c>
-      <c r="N24" s="19">
-        <v>250</v>
-      </c>
-      <c r="O24" s="19">
-        <f>C5*I24</f>
-        <v>1.84</v>
-      </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19">
-        <v>100</v>
-      </c>
-      <c r="R24" s="19">
-        <f t="shared" si="0"/>
-        <v>273.05599999999998</v>
-      </c>
-      <c r="S24" s="70"/>
-      <c r="T24" s="30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="19">
-        <v>17</v>
-      </c>
-      <c r="B25" s="19">
-        <v>145</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19">
-        <v>17</v>
-      </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="20">
-        <v>1.8</v>
-      </c>
-      <c r="I25" s="20">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="20">
-        <v>0</v>
-      </c>
-      <c r="L25" s="19">
-        <f>1+K25*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M25" s="19">
-        <f>(B5+B25)*H25*L25*E5</f>
-        <v>266.39999999999998</v>
-      </c>
-      <c r="N25" s="19">
-        <v>266</v>
-      </c>
-      <c r="O25" s="19">
-        <f>C5*I25</f>
-        <v>1.84</v>
-      </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19">
-        <v>100</v>
-      </c>
-      <c r="R25" s="19">
-        <f t="shared" si="0"/>
-        <v>306.17599999999999</v>
-      </c>
-      <c r="S25" s="70"/>
-      <c r="T25" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="U25" s="21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="22">
-        <v>18</v>
-      </c>
-      <c r="B26" s="22">
-        <v>270</v>
-      </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22">
-        <v>18</v>
-      </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23">
-        <v>1.9</v>
-      </c>
-      <c r="I26" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="23">
-        <v>0</v>
-      </c>
-      <c r="L26" s="22">
-        <f>1+K26*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M26" s="22">
-        <f>(B5+B26)*H26*L26*E5</f>
-        <v>518.70000000000005</v>
-      </c>
-      <c r="N26" s="22">
-        <v>520</v>
-      </c>
-      <c r="O26" s="22">
-        <f>C5*I26</f>
-        <v>1.92</v>
-      </c>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22">
-        <v>200</v>
-      </c>
-      <c r="R26" s="22">
-        <f t="shared" si="0"/>
-        <v>611.904</v>
-      </c>
-      <c r="S26" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="T26" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="U26" s="31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="22">
-        <v>19</v>
-      </c>
-      <c r="B27" s="22">
-        <v>295</v>
-      </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22">
-        <v>19</v>
-      </c>
-      <c r="G27" s="22"/>
-      <c r="H27" s="23">
-        <v>1.9</v>
-      </c>
-      <c r="I27" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="J27" s="22"/>
-      <c r="K27" s="23">
-        <v>0</v>
-      </c>
-      <c r="L27" s="22">
-        <f>1+K27*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M27" s="22">
-        <f>(B5+B27)*H27*L27*E5</f>
-        <v>566.20000000000005</v>
-      </c>
-      <c r="N27" s="22">
-        <v>568</v>
-      </c>
-      <c r="O27" s="22">
-        <f>C5*I27</f>
-        <v>1.92</v>
-      </c>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22">
-        <v>200</v>
-      </c>
-      <c r="R27" s="22">
-        <f t="shared" si="0"/>
-        <v>703.10400000000004</v>
-      </c>
-      <c r="S27" s="72"/>
-      <c r="T27" s="31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="22">
-        <v>20</v>
-      </c>
-      <c r="B28" s="22">
-        <v>325</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22">
-        <v>20</v>
-      </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="23">
-        <v>1.9</v>
-      </c>
-      <c r="I28" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="23">
-        <v>0</v>
-      </c>
-      <c r="L28" s="22">
-        <f>1+K28*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M28" s="22">
-        <f>(B5+B28)*H28*L28*E5</f>
-        <v>623.20000000000005</v>
-      </c>
-      <c r="N28" s="22">
-        <v>618</v>
-      </c>
-      <c r="O28" s="22">
-        <f>C5*I28</f>
-        <v>1.92</v>
-      </c>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22">
-        <v>200</v>
-      </c>
-      <c r="R28" s="22">
-        <f t="shared" si="0"/>
-        <v>812.54399999999998</v>
-      </c>
-      <c r="S28" s="72"/>
-      <c r="T28" s="31" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="22">
-        <v>21</v>
-      </c>
-      <c r="B29" s="22">
-        <v>350</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22">
-        <v>21</v>
-      </c>
-      <c r="G29" s="22"/>
-      <c r="H29" s="23">
-        <v>2</v>
-      </c>
-      <c r="I29" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="23">
-        <v>0</v>
-      </c>
-      <c r="L29" s="22">
-        <f>1+K29*F5</f>
-        <v>1</v>
-      </c>
-      <c r="M29" s="22">
-        <f>(B5+B29)*H29*L29*E5</f>
-        <v>706</v>
-      </c>
-      <c r="N29" s="22">
-        <v>710</v>
-      </c>
-      <c r="O29" s="22">
-        <f>C5*I29</f>
-        <v>1.92</v>
-      </c>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22">
-        <v>200</v>
-      </c>
-      <c r="R29" s="22">
-        <f t="shared" si="0"/>
-        <v>971.52</v>
-      </c>
-      <c r="S29" s="72"/>
-      <c r="T29" s="32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A32" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A33" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="46" t="s">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="52" t="s">
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="52"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A34" s="41" t="s">
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="54"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A34" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
       <c r="D34" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A35" s="54" t="s">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="D35" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="E35" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="F35" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="G35" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54" t="s">
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54" t="s">
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54" t="s">
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54" t="s">
+      <c r="Q35" s="53"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="Q35" s="54"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A36" s="54"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>5</v>
-      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
       <c r="G36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="66" t="s">
         <v>4</v>
       </c>
       <c r="I36" s="3" t="s">
@@ -4492,7 +4294,7 @@
       <c r="J36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" s="66" t="s">
         <v>4</v>
       </c>
       <c r="L36" s="3" t="s">
@@ -4501,1306 +4303,1434 @@
       <c r="M36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="N36" s="66" t="s">
         <v>4</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P36" s="54"/>
-      <c r="Q36" s="54"/>
-    </row>
-    <row r="37" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13">
+      <c r="P36" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q36" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="25">
         <v>1</v>
       </c>
-      <c r="B37" s="33">
+      <c r="E37" s="59">
         <v>0</v>
       </c>
-      <c r="C37" s="33">
+      <c r="F37" s="59">
         <v>0</v>
       </c>
-      <c r="D37" s="34">
+      <c r="G37" s="65">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E37" s="13">
-        <f>CEILING(B37*D37,1)</f>
+      <c r="H37" s="67">
+        <f>CEILING(E37*G37,1)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="13">
-        <f>C37/4</f>
+      <c r="I37" s="25">
+        <f>F37/4</f>
         <v>0</v>
       </c>
-      <c r="G37" s="34">
+      <c r="J37" s="65">
         <v>0.33300000000000002</v>
       </c>
-      <c r="H37" s="13">
-        <f>CEILING(B37*G37,1)</f>
+      <c r="K37" s="67">
+        <f>CEILING(E37*J37,1)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="13">
-        <f>C37/4</f>
+      <c r="L37" s="25">
+        <f>F37/4</f>
         <v>0</v>
       </c>
-      <c r="J37" s="34">
+      <c r="M37" s="65">
         <v>0.29099999999999998</v>
       </c>
-      <c r="K37" s="13">
-        <f>CEILING(B37*J37,1)</f>
+      <c r="N37" s="67">
+        <f>CEILING(E37*M37,1)</f>
         <v>0</v>
       </c>
-      <c r="L37" s="13">
-        <f>C37/4</f>
+      <c r="O37" s="25">
+        <f>F37/4</f>
         <v>0</v>
       </c>
-      <c r="M37" s="34">
+      <c r="P37" s="65">
         <v>0.16600000000000001</v>
       </c>
-      <c r="N37" s="13">
-        <f>CEILING(B37*M37,1)</f>
+      <c r="Q37" s="67">
+        <f>CEILING(E37*P37,1)</f>
         <v>0</v>
       </c>
-      <c r="O37" s="13">
-        <f>C37/4</f>
+      <c r="R37" s="25">
+        <f>F37/4</f>
         <v>0</v>
       </c>
-      <c r="P37" s="55">
-        <f>E37+H37+K37+N37</f>
+      <c r="S37" s="25">
+        <f>H37+K37+N37+Q37</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="56"/>
-    </row>
-    <row r="38" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13">
+    </row>
+    <row r="38" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="25"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="25">
         <v>2</v>
       </c>
-      <c r="B38" s="33">
+      <c r="E38" s="59">
         <v>4</v>
       </c>
-      <c r="C38" s="33">
+      <c r="F38" s="59">
         <v>0</v>
       </c>
-      <c r="D38" s="34">
+      <c r="G38" s="65">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E38" s="13">
-        <f t="shared" ref="E38:E57" si="1">CEILING(B38*D38,1)</f>
+      <c r="H38" s="67">
+        <f t="shared" ref="H38:H57" si="0">CEILING(E38*G38,1)</f>
         <v>1</v>
       </c>
-      <c r="F38" s="13">
-        <f t="shared" ref="F38:F57" si="2">C38/4</f>
+      <c r="I38" s="25">
+        <f t="shared" ref="I38:I57" si="1">F38/4</f>
         <v>0</v>
       </c>
-      <c r="G38" s="34">
+      <c r="J38" s="65">
         <v>0.33300000000000002</v>
       </c>
-      <c r="H38" s="13">
-        <f t="shared" ref="H38:H57" si="3">CEILING(B38*G38,1)</f>
+      <c r="K38" s="67">
+        <f t="shared" ref="K38:K57" si="2">CEILING(E38*J38,1)</f>
         <v>2</v>
       </c>
-      <c r="I38" s="13">
-        <f t="shared" ref="I38:I57" si="4">C38/4</f>
+      <c r="L38" s="25">
+        <f t="shared" ref="L38:L57" si="3">F38/4</f>
         <v>0</v>
       </c>
-      <c r="J38" s="34">
+      <c r="M38" s="65">
         <v>0.29099999999999998</v>
       </c>
-      <c r="K38" s="13">
-        <f t="shared" ref="K38:K57" si="5">CEILING(B38*J38,1)</f>
+      <c r="N38" s="67">
+        <f t="shared" ref="N38:N57" si="4">CEILING(E38*M38,1)</f>
         <v>2</v>
       </c>
-      <c r="L38" s="13">
-        <f t="shared" ref="L38:L57" si="6">C38/4</f>
+      <c r="O38" s="25">
+        <f t="shared" ref="O38:O57" si="5">F38/4</f>
         <v>0</v>
       </c>
-      <c r="M38" s="34">
+      <c r="P38" s="65">
         <v>0.16600000000000001</v>
       </c>
-      <c r="N38" s="13">
-        <f t="shared" ref="N38:N57" si="7">CEILING(B38*M38,1)</f>
+      <c r="Q38" s="67">
+        <f t="shared" ref="Q38:Q57" si="6">CEILING(E38*P38,1)</f>
         <v>1</v>
       </c>
-      <c r="O38" s="13">
-        <f t="shared" ref="O38:O57" si="8">C38/4</f>
+      <c r="R38" s="25">
+        <f t="shared" ref="R38:R57" si="7">F38/4</f>
         <v>0</v>
       </c>
-      <c r="P38" s="55">
-        <f t="shared" ref="P38:P57" si="9">E38+H38+K38+N38</f>
+      <c r="S38" s="25">
+        <f t="shared" ref="S38:S57" si="8">H38+K38+N38+Q38</f>
         <v>6</v>
       </c>
-      <c r="Q38" s="56"/>
-    </row>
-    <row r="39" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13">
+    </row>
+    <row r="39" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="25"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="25">
         <v>3</v>
       </c>
-      <c r="B39" s="33">
+      <c r="E39" s="59">
         <v>8</v>
       </c>
-      <c r="C39" s="33">
+      <c r="F39" s="59">
         <v>0</v>
       </c>
-      <c r="D39" s="34">
+      <c r="G39" s="65">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E39" s="13">
+      <c r="H39" s="67">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I39" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="65">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K39" s="67">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L39" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="65">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N39" s="67">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="O39" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="65">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q39" s="67">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="R39" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="25">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="28"/>
+      <c r="D40" s="13">
+        <v>4</v>
+      </c>
+      <c r="E40" s="28">
+        <v>8</v>
+      </c>
+      <c r="F40" s="28">
+        <v>4</v>
+      </c>
+      <c r="G40" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H40" s="68">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I40" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="29">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K40" s="68">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L40" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M40" s="29">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N40" s="68">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="O40" s="13">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="P40" s="29">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q40" s="68">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="R40" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S40" s="13">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="T40"/>
+    </row>
+    <row r="41" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="38"/>
+      <c r="B41" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="13">
+        <v>5</v>
+      </c>
+      <c r="E41" s="28">
+        <v>12</v>
+      </c>
+      <c r="F41" s="28">
+        <v>4</v>
+      </c>
+      <c r="G41" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H41" s="68">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I41" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J41" s="29">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K41" s="68">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L41" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M41" s="29">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N41" s="68">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="O41" s="13">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="P41" s="29">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q41" s="68">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="R41" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S41" s="13">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="T41"/>
+    </row>
+    <row r="42" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="38"/>
+      <c r="B42" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="13">
+        <v>6</v>
+      </c>
+      <c r="E42" s="28">
+        <v>16</v>
+      </c>
+      <c r="F42" s="28">
+        <v>4</v>
+      </c>
+      <c r="G42" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H42" s="68">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I42" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J42" s="29">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K42" s="68">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L42" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M42" s="29">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N42" s="68">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="O42" s="13">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="P42" s="29">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q42" s="68">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="R42" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S42" s="13">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="T42"/>
+    </row>
+    <row r="43" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="38"/>
+      <c r="B43" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="13">
+        <v>7</v>
+      </c>
+      <c r="E43" s="28">
+        <v>16</v>
+      </c>
+      <c r="F43" s="28">
+        <v>8</v>
+      </c>
+      <c r="G43" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H43" s="68">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I43" s="13">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F39" s="13">
+      <c r="J43" s="29">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K43" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="34">
+        <v>6</v>
+      </c>
+      <c r="L43" s="13">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M43" s="29">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N43" s="68">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="O43" s="13">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P43" s="29">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q43" s="68">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="R43" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S43" s="13">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="T43"/>
+    </row>
+    <row r="44" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="38"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="13">
+        <v>8</v>
+      </c>
+      <c r="E44" s="28">
+        <v>20</v>
+      </c>
+      <c r="F44" s="28">
+        <v>8</v>
+      </c>
+      <c r="G44" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H44" s="68">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I44" s="13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J44" s="29">
         <v>0.33300000000000002</v>
       </c>
-      <c r="H39" s="13">
+      <c r="K44" s="68">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="L44" s="13">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M44" s="29">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N44" s="68">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="O44" s="13">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P44" s="29">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q44" s="68">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="R44" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S44" s="13">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
+      <c r="T44"/>
+    </row>
+    <row r="45" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="30"/>
+      <c r="D45" s="16">
+        <v>9</v>
+      </c>
+      <c r="E45" s="30">
+        <v>24</v>
+      </c>
+      <c r="F45" s="30">
+        <v>8</v>
+      </c>
+      <c r="G45" s="31">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H45" s="69">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I45" s="16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J45" s="31">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K45" s="69">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="L45" s="16">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M45" s="31">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N45" s="69">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="O45" s="16">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P45" s="31">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q45" s="69">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="R45" s="16">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S45" s="16">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="T45"/>
+    </row>
+    <row r="46" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="39"/>
+      <c r="B46" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="30"/>
+      <c r="D46" s="16">
+        <v>10</v>
+      </c>
+      <c r="E46" s="30">
+        <v>28</v>
+      </c>
+      <c r="F46" s="30">
+        <v>12</v>
+      </c>
+      <c r="G46" s="31">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H46" s="69">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I46" s="16">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J46" s="31">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K46" s="69">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="L46" s="16">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I39" s="13">
+      <c r="M46" s="31">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N46" s="69">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="34">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K39" s="13">
+        <v>9</v>
+      </c>
+      <c r="O46" s="16">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="L39" s="13">
+      <c r="P46" s="31">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q46" s="69">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="34">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N39" s="13">
+        <v>5</v>
+      </c>
+      <c r="R46" s="16">
         <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="O39" s="13">
+        <v>3</v>
+      </c>
+      <c r="S46" s="16">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="P39" s="55">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="Q39" s="56"/>
-    </row>
-    <row r="40" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13">
-        <v>4</v>
-      </c>
-      <c r="B40" s="33">
-        <v>8</v>
-      </c>
-      <c r="C40" s="33">
-        <v>4</v>
-      </c>
-      <c r="D40" s="34">
+        <v>30</v>
+      </c>
+      <c r="T46"/>
+    </row>
+    <row r="47" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="39"/>
+      <c r="B47" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="30"/>
+      <c r="D47" s="16">
+        <v>11</v>
+      </c>
+      <c r="E47" s="30">
+        <v>32</v>
+      </c>
+      <c r="F47" s="30">
+        <v>12</v>
+      </c>
+      <c r="G47" s="31">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E40" s="13">
+      <c r="H47" s="69">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I47" s="16">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="F40" s="13">
+        <v>3</v>
+      </c>
+      <c r="J47" s="31">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K47" s="69">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G40" s="34">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H40" s="13">
+        <v>11</v>
+      </c>
+      <c r="L47" s="16">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="I40" s="13">
+      <c r="M47" s="31">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N47" s="69">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="J40" s="34">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K40" s="13">
+        <v>10</v>
+      </c>
+      <c r="O47" s="16">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="L40" s="13">
+      <c r="P47" s="31">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q47" s="69">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M40" s="34">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N40" s="13">
+        <v>6</v>
+      </c>
+      <c r="R47" s="16">
         <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="O40" s="13">
+        <v>3</v>
+      </c>
+      <c r="S47" s="16">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="P40" s="55">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="Q40" s="56"/>
-    </row>
-    <row r="41" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13">
-        <v>5</v>
-      </c>
-      <c r="B41" s="33">
+        <v>34</v>
+      </c>
+      <c r="T47"/>
+    </row>
+    <row r="48" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="39"/>
+      <c r="B48" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="30"/>
+      <c r="D48" s="16">
         <v>12</v>
       </c>
-      <c r="C41" s="33">
-        <v>4</v>
-      </c>
-      <c r="D41" s="34">
+      <c r="E48" s="30">
+        <v>36</v>
+      </c>
+      <c r="F48" s="30">
+        <v>12</v>
+      </c>
+      <c r="G48" s="31">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E41" s="13">
+      <c r="H48" s="69">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="I48" s="16">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F41" s="13">
+      <c r="J48" s="31">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K48" s="69">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G41" s="34">
+        <v>12</v>
+      </c>
+      <c r="L48" s="16">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M48" s="31">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N48" s="69">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="O48" s="16">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P48" s="31">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q48" s="69">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="R48" s="16">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S48" s="16">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+      <c r="T48"/>
+    </row>
+    <row r="49" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="39"/>
+      <c r="B49" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="16">
+        <v>13</v>
+      </c>
+      <c r="E49" s="30">
+        <v>40</v>
+      </c>
+      <c r="F49" s="30">
+        <v>12</v>
+      </c>
+      <c r="G49" s="31">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H49" s="69">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I49" s="16">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J49" s="31">
         <v>0.33300000000000002</v>
       </c>
-      <c r="H41" s="13">
+      <c r="K49" s="69">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="L49" s="16">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M49" s="31">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N49" s="69">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="O49" s="16">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P49" s="31">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q49" s="69">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="R49" s="16">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S49" s="16">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+      <c r="T49"/>
+    </row>
+    <row r="50" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="39"/>
+      <c r="B50" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="16">
+        <v>14</v>
+      </c>
+      <c r="E50" s="30">
+        <v>40</v>
+      </c>
+      <c r="F50" s="30">
+        <v>16</v>
+      </c>
+      <c r="G50" s="31">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H50" s="69">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I50" s="16">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J50" s="31">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K50" s="69">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="L50" s="16">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I41" s="13">
+      <c r="M50" s="31">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N50" s="69">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="J41" s="34">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K41" s="13">
+        <v>12</v>
+      </c>
+      <c r="O50" s="16">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="L41" s="13">
+      <c r="P50" s="31">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q50" s="69">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M41" s="34">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N41" s="13">
+        <v>7</v>
+      </c>
+      <c r="R50" s="16">
         <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="O41" s="13">
+        <v>4</v>
+      </c>
+      <c r="S50" s="16">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="P41" s="55">
-        <f t="shared" si="9"/>
-        <v>13</v>
-      </c>
-      <c r="Q41" s="56"/>
-    </row>
-    <row r="42" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="13">
-        <v>6</v>
-      </c>
-      <c r="B42" s="33">
+        <v>42</v>
+      </c>
+      <c r="T50"/>
+    </row>
+    <row r="51" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="32"/>
+      <c r="D51" s="19">
+        <v>15</v>
+      </c>
+      <c r="E51" s="32">
+        <v>44</v>
+      </c>
+      <c r="F51" s="32">
         <v>16</v>
       </c>
-      <c r="C42" s="33">
-        <v>4</v>
-      </c>
-      <c r="D42" s="34">
+      <c r="G51" s="33">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E42" s="13">
+      <c r="H51" s="70">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I51" s="19">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F42" s="13">
+      <c r="J51" s="33">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K51" s="70">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G42" s="34">
+        <v>15</v>
+      </c>
+      <c r="L51" s="19">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M51" s="33">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N51" s="70">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="O51" s="19">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="P51" s="33">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q51" s="70">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="R51" s="19">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="S51" s="19">
+        <f t="shared" si="8"/>
+        <v>46</v>
+      </c>
+      <c r="T51"/>
+    </row>
+    <row r="52" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="40"/>
+      <c r="B52" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="32"/>
+      <c r="D52" s="19">
+        <v>16</v>
+      </c>
+      <c r="E52" s="32">
+        <v>52</v>
+      </c>
+      <c r="F52" s="32">
+        <v>20</v>
+      </c>
+      <c r="G52" s="33">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H52" s="70">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I52" s="19">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J52" s="33">
         <v>0.33300000000000002</v>
       </c>
-      <c r="H42" s="13">
+      <c r="K52" s="70">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="L52" s="19">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M52" s="33">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N52" s="70">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="O52" s="19">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="P52" s="33">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q52" s="70">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="R52" s="19">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S52" s="19">
+        <f t="shared" si="8"/>
+        <v>54</v>
+      </c>
+      <c r="T52"/>
+    </row>
+    <row r="53" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="40"/>
+      <c r="B53" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" s="19">
+        <v>17</v>
+      </c>
+      <c r="E53" s="32">
+        <v>56</v>
+      </c>
+      <c r="F53" s="32">
+        <v>24</v>
+      </c>
+      <c r="G53" s="33">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H53" s="70">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I53" s="19">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J53" s="33">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K53" s="70">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="L53" s="19">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="I42" s="13">
+      <c r="M53" s="33">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N53" s="70">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="J42" s="34">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K42" s="13">
+        <v>17</v>
+      </c>
+      <c r="O53" s="19">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="L42" s="13">
+        <v>6</v>
+      </c>
+      <c r="P53" s="33">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q53" s="70">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M42" s="34">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N42" s="13">
+        <v>10</v>
+      </c>
+      <c r="R53" s="19">
         <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="O42" s="13">
+        <v>6</v>
+      </c>
+      <c r="S53" s="19">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="P42" s="55">
-        <f t="shared" si="9"/>
+        <v>58</v>
+      </c>
+      <c r="T53"/>
+    </row>
+    <row r="54" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="22">
         <v>18</v>
       </c>
-      <c r="Q42" s="56"/>
-    </row>
-    <row r="43" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13">
+      <c r="E54" s="34">
+        <v>60</v>
+      </c>
+      <c r="F54" s="34">
+        <v>28</v>
+      </c>
+      <c r="G54" s="35">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H54" s="71">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="I54" s="22">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B43" s="33">
-        <v>16</v>
-      </c>
-      <c r="C43" s="33">
-        <v>8</v>
-      </c>
-      <c r="D43" s="34">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E43" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="F43" s="13">
+      <c r="J54" s="35">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K54" s="71">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="G43" s="34">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H43" s="13">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="I43" s="13">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="J43" s="34">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K43" s="13">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="L43" s="13">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="M43" s="34">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N43" s="13">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="O43" s="13">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="P43" s="55">
-        <f t="shared" si="9"/>
-        <v>18</v>
-      </c>
-      <c r="Q43" s="56"/>
-    </row>
-    <row r="44" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13">
-        <v>8</v>
-      </c>
-      <c r="B44" s="33">
         <v>20</v>
       </c>
-      <c r="C44" s="33">
-        <v>8</v>
-      </c>
-      <c r="D44" s="34">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E44" s="13">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="F44" s="13">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="G44" s="34">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H44" s="13">
+      <c r="L54" s="22">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="I44" s="13">
+      <c r="M54" s="35">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N54" s="71">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="J44" s="34">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K44" s="13">
+        <v>18</v>
+      </c>
+      <c r="O54" s="22">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="L44" s="13">
+        <v>7</v>
+      </c>
+      <c r="P54" s="35">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q54" s="71">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="M44" s="34">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N44" s="13">
+        <v>10</v>
+      </c>
+      <c r="R54" s="22">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="O44" s="13">
+        <v>7</v>
+      </c>
+      <c r="S54" s="22">
         <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="P44" s="55">
-        <f t="shared" si="9"/>
+        <v>61</v>
+      </c>
+      <c r="T54"/>
+    </row>
+    <row r="55" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="41"/>
+      <c r="B55" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="34"/>
+      <c r="D55" s="22">
+        <v>19</v>
+      </c>
+      <c r="E55" s="34">
+        <v>64</v>
+      </c>
+      <c r="F55" s="34">
+        <v>32</v>
+      </c>
+      <c r="G55" s="35">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H55" s="71">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="I55" s="22">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="J55" s="35">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K55" s="71">
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="Q44" s="56"/>
-    </row>
-    <row r="45" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="16">
-        <v>9</v>
-      </c>
-      <c r="B45" s="35">
-        <v>24</v>
-      </c>
-      <c r="C45" s="35">
-        <v>8</v>
-      </c>
-      <c r="D45" s="36">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E45" s="16">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="F45" s="16">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="G45" s="36">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H45" s="16">
+      <c r="L55" s="22">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="I45" s="16">
+      <c r="M55" s="35">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N55" s="71">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="J45" s="36">
+        <v>19</v>
+      </c>
+      <c r="O55" s="22">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="P55" s="35">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q55" s="71">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="R55" s="22">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="S55" s="22">
+        <f t="shared" si="8"/>
+        <v>66</v>
+      </c>
+      <c r="T55"/>
+    </row>
+    <row r="56" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="41"/>
+      <c r="B56" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="34"/>
+      <c r="D56" s="22">
+        <v>20</v>
+      </c>
+      <c r="E56" s="34">
+        <v>68</v>
+      </c>
+      <c r="F56" s="34">
+        <v>36</v>
+      </c>
+      <c r="G56" s="35">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H56" s="71">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I56" s="22">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="J56" s="35">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K56" s="71">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="L56" s="22">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="M56" s="35">
         <v>0.29099999999999998</v>
       </c>
-      <c r="K45" s="16">
+      <c r="N56" s="71">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="O56" s="22">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="L45" s="16">
+        <v>9</v>
+      </c>
+      <c r="P56" s="35">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q56" s="71">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="M45" s="36">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N45" s="16">
+        <v>12</v>
+      </c>
+      <c r="R56" s="22">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="O45" s="16">
+        <v>9</v>
+      </c>
+      <c r="S56" s="22">
         <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="P45" s="57">
-        <f t="shared" si="9"/>
+        <v>70</v>
+      </c>
+      <c r="T56"/>
+    </row>
+    <row r="57" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="41"/>
+      <c r="B57" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="34"/>
+      <c r="D57" s="22">
+        <v>21</v>
+      </c>
+      <c r="E57" s="34">
+        <v>72</v>
+      </c>
+      <c r="F57" s="34">
+        <v>40</v>
+      </c>
+      <c r="G57" s="35">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H57" s="71">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I57" s="22">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J57" s="35">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K57" s="71">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="Q45" s="58"/>
-    </row>
-    <row r="46" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="16">
-        <v>10</v>
-      </c>
-      <c r="B46" s="35">
-        <v>28</v>
-      </c>
-      <c r="C46" s="35">
-        <v>12</v>
-      </c>
-      <c r="D46" s="36">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E46" s="16">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="F46" s="16">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G46" s="36">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H46" s="16">
+      <c r="L57" s="22">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="I46" s="16">
+      <c r="M57" s="35">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="N57" s="71">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="J46" s="36">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K46" s="16">
-        <f t="shared" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="L46" s="16">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M46" s="36">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N46" s="16">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="O46" s="16">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="P46" s="57">
-        <f t="shared" si="9"/>
-        <v>30</v>
-      </c>
-      <c r="Q46" s="58"/>
-    </row>
-    <row r="47" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="16">
-        <v>11</v>
-      </c>
-      <c r="B47" s="35">
-        <v>32</v>
-      </c>
-      <c r="C47" s="35">
-        <v>12</v>
-      </c>
-      <c r="D47" s="36">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E47" s="16">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="F47" s="16">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G47" s="36">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H47" s="16">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="I47" s="16">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="J47" s="36">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K47" s="16">
+        <v>21</v>
+      </c>
+      <c r="O57" s="22">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="L47" s="16">
+      <c r="P57" s="35">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Q57" s="71">
         <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M47" s="36">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N47" s="16">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="O47" s="16">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="P47" s="57">
-        <f t="shared" si="9"/>
-        <v>34</v>
-      </c>
-      <c r="Q47" s="58"/>
-    </row>
-    <row r="48" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="16">
         <v>12</v>
       </c>
-      <c r="B48" s="35">
-        <v>36</v>
-      </c>
-      <c r="C48" s="35">
-        <v>12</v>
-      </c>
-      <c r="D48" s="36">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E48" s="16">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="F48" s="16">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G48" s="36">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H48" s="16">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="I48" s="16">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="J48" s="36">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K48" s="16">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="L48" s="16">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M48" s="36">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N48" s="16">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="O48" s="16">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="P48" s="57">
-        <f t="shared" si="9"/>
-        <v>37</v>
-      </c>
-      <c r="Q48" s="58"/>
-    </row>
-    <row r="49" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="16">
-        <v>13</v>
-      </c>
-      <c r="B49" s="35">
-        <v>40</v>
-      </c>
-      <c r="C49" s="35">
-        <v>12</v>
-      </c>
-      <c r="D49" s="36">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E49" s="16">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F49" s="16">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G49" s="36">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H49" s="16">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="I49" s="16">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="J49" s="36">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K49" s="16">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="L49" s="16">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M49" s="36">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N49" s="16">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="O49" s="16">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="P49" s="57">
-        <f t="shared" si="9"/>
-        <v>42</v>
-      </c>
-      <c r="Q49" s="58"/>
-    </row>
-    <row r="50" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="16">
-        <v>14</v>
-      </c>
-      <c r="B50" s="35">
-        <v>40</v>
-      </c>
-      <c r="C50" s="35">
-        <v>16</v>
-      </c>
-      <c r="D50" s="36">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E50" s="16">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F50" s="16">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G50" s="36">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H50" s="16">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="I50" s="16">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="J50" s="36">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K50" s="16">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="L50" s="16">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="M50" s="36">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N50" s="16">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="O50" s="16">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="P50" s="57">
-        <f t="shared" si="9"/>
-        <v>42</v>
-      </c>
-      <c r="Q50" s="58"/>
-    </row>
-    <row r="51" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="19">
-        <v>15</v>
-      </c>
-      <c r="B51" s="37">
-        <v>44</v>
-      </c>
-      <c r="C51" s="37">
-        <v>16</v>
-      </c>
-      <c r="D51" s="38">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E51" s="19">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F51" s="19">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G51" s="38">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H51" s="19">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="I51" s="19">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="J51" s="38">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K51" s="19">
-        <f t="shared" si="5"/>
-        <v>13</v>
-      </c>
-      <c r="L51" s="19">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="M51" s="38">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N51" s="19">
-        <f t="shared" si="7"/>
-        <v>8</v>
-      </c>
-      <c r="O51" s="19">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="P51" s="59">
-        <f t="shared" si="9"/>
-        <v>46</v>
-      </c>
-      <c r="Q51" s="60"/>
-    </row>
-    <row r="52" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="19">
-        <v>16</v>
-      </c>
-      <c r="B52" s="37">
-        <v>52</v>
-      </c>
-      <c r="C52" s="37">
-        <v>20</v>
-      </c>
-      <c r="D52" s="38">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E52" s="19">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="F52" s="19">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="G52" s="38">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H52" s="19">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="I52" s="19">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="J52" s="38">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K52" s="19">
-        <f t="shared" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="L52" s="19">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="M52" s="38">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N52" s="19">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="O52" s="19">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="P52" s="59">
-        <f t="shared" si="9"/>
-        <v>54</v>
-      </c>
-      <c r="Q52" s="60"/>
-    </row>
-    <row r="53" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="19">
-        <v>17</v>
-      </c>
-      <c r="B53" s="37">
-        <v>56</v>
-      </c>
-      <c r="C53" s="37">
-        <v>24</v>
-      </c>
-      <c r="D53" s="38">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E53" s="19">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="F53" s="19">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="G53" s="38">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H53" s="19">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="I53" s="19">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="J53" s="38">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K53" s="19">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="L53" s="19">
-        <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="M53" s="38">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N53" s="19">
+      <c r="R57" s="22">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="O53" s="19">
+      <c r="S57" s="22">
         <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="P53" s="59">
-        <f t="shared" si="9"/>
-        <v>58</v>
-      </c>
-      <c r="Q53" s="60"/>
-    </row>
-    <row r="54" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="22">
-        <v>18</v>
-      </c>
-      <c r="B54" s="39">
-        <v>60</v>
-      </c>
-      <c r="C54" s="39">
-        <v>28</v>
-      </c>
-      <c r="D54" s="40">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E54" s="22">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="F54" s="22">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="G54" s="40">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H54" s="22">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="I54" s="22">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="J54" s="40">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K54" s="22">
-        <f t="shared" si="5"/>
-        <v>18</v>
-      </c>
-      <c r="L54" s="22">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="M54" s="40">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N54" s="22">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O54" s="22">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="P54" s="61">
-        <f t="shared" si="9"/>
-        <v>61</v>
-      </c>
-      <c r="Q54" s="62"/>
-    </row>
-    <row r="55" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="22">
-        <v>19</v>
-      </c>
-      <c r="B55" s="39">
-        <v>64</v>
-      </c>
-      <c r="C55" s="39">
-        <v>32</v>
-      </c>
-      <c r="D55" s="40">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E55" s="22">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="F55" s="22">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="G55" s="40">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H55" s="22">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="I55" s="22">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="J55" s="40">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K55" s="22">
-        <f t="shared" si="5"/>
-        <v>19</v>
-      </c>
-      <c r="L55" s="22">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="M55" s="40">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N55" s="22">
-        <f t="shared" si="7"/>
-        <v>11</v>
-      </c>
-      <c r="O55" s="22">
-        <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="P55" s="61">
-        <f t="shared" si="9"/>
-        <v>66</v>
-      </c>
-      <c r="Q55" s="62"/>
-    </row>
-    <row r="56" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="22">
-        <v>20</v>
-      </c>
-      <c r="B56" s="39">
-        <v>68</v>
-      </c>
-      <c r="C56" s="39">
-        <v>36</v>
-      </c>
-      <c r="D56" s="40">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E56" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="F56" s="22">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="G56" s="40">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H56" s="22">
-        <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-      <c r="I56" s="22">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="J56" s="40">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K56" s="22">
-        <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="L56" s="22">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="M56" s="40">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N56" s="22">
-        <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-      <c r="O56" s="22">
-        <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="P56" s="61">
-        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="T57"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A82" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A83" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="Q56" s="62"/>
-    </row>
-    <row r="57" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="22">
-        <v>21</v>
-      </c>
-      <c r="B57" s="39">
-        <v>72</v>
-      </c>
-      <c r="C57" s="39">
-        <v>40</v>
-      </c>
-      <c r="D57" s="40">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E57" s="22">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="F57" s="22">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="G57" s="40">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H57" s="22">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="I57" s="22">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="J57" s="40">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="K57" s="22">
-        <f t="shared" si="5"/>
-        <v>21</v>
-      </c>
-      <c r="L57" s="22">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="M57" s="40">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="N57" s="22">
-        <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-      <c r="O57" s="22">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="P57" s="61">
-        <f t="shared" si="9"/>
-        <v>72</v>
-      </c>
-      <c r="Q57" s="62"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A82" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B82" s="45"/>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="45"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="45"/>
-      <c r="J82" s="45"/>
-      <c r="K82" s="45"/>
-      <c r="L82" s="45"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A83" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B83" s="52"/>
-      <c r="C83" s="52"/>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="46" t="s">
+      <c r="B83" s="54"/>
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="54"/>
+      <c r="G83" s="54"/>
+      <c r="H83" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="51"/>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5839,10 +5769,10 @@
       <c r="J84" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K84" s="42">
+      <c r="K84" s="45">
         <v>2</v>
       </c>
-      <c r="L84" s="42">
+      <c r="L84" s="45">
         <f>I85*(H85-K84)</f>
         <v>0</v>
       </c>
@@ -5856,12 +5786,12 @@
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="42"/>
-      <c r="H85" s="42"/>
-      <c r="I85" s="42"/>
-      <c r="J85" s="44"/>
-      <c r="K85" s="44"/>
-      <c r="L85" s="44"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45"/>
+      <c r="J85" s="47"/>
+      <c r="K85" s="47"/>
+      <c r="L85" s="47"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
@@ -5872,14 +5802,14 @@
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="43"/>
-      <c r="H86" s="43"/>
-      <c r="I86" s="43"/>
-      <c r="J86" s="54"/>
-      <c r="K86" s="42">
+      <c r="G86" s="46"/>
+      <c r="H86" s="46"/>
+      <c r="I86" s="46"/>
+      <c r="J86" s="53"/>
+      <c r="K86" s="45">
         <v>10</v>
       </c>
-      <c r="L86" s="42">
+      <c r="L86" s="45">
         <f>I85*(H85-K86)</f>
         <v>0</v>
       </c>
@@ -5893,12 +5823,12 @@
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="43"/>
-      <c r="H87" s="43"/>
-      <c r="I87" s="43"/>
-      <c r="J87" s="54"/>
-      <c r="K87" s="44"/>
-      <c r="L87" s="44"/>
+      <c r="G87" s="46"/>
+      <c r="H87" s="46"/>
+      <c r="I87" s="46"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="47"/>
+      <c r="L87" s="47"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A88" s="3" t="s">
@@ -5909,14 +5839,14 @@
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="43"/>
-      <c r="H88" s="43"/>
-      <c r="I88" s="43"/>
-      <c r="J88" s="54"/>
-      <c r="K88" s="42">
+      <c r="G88" s="46"/>
+      <c r="H88" s="46"/>
+      <c r="I88" s="46"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="45">
         <v>25</v>
       </c>
-      <c r="L88" s="42">
+      <c r="L88" s="45">
         <f>I85*(H85-K88)</f>
         <v>0</v>
       </c>
@@ -5930,12 +5860,12 @@
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-      <c r="G89" s="43"/>
-      <c r="H89" s="43"/>
-      <c r="I89" s="43"/>
-      <c r="J89" s="54"/>
-      <c r="K89" s="44"/>
-      <c r="L89" s="44"/>
+      <c r="G89" s="46"/>
+      <c r="H89" s="46"/>
+      <c r="I89" s="46"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="47"/>
+      <c r="L89" s="47"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A90" s="3" t="s">
@@ -5946,14 +5876,14 @@
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
-      <c r="G90" s="43"/>
-      <c r="H90" s="43"/>
-      <c r="I90" s="43"/>
-      <c r="J90" s="54"/>
-      <c r="K90" s="42">
+      <c r="G90" s="46"/>
+      <c r="H90" s="46"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="45">
         <v>100</v>
       </c>
-      <c r="L90" s="42">
+      <c r="L90" s="45">
         <f>I85*(H85-K90)</f>
         <v>0</v>
       </c>
@@ -5967,12 +5897,12 @@
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="43"/>
-      <c r="H91" s="43"/>
-      <c r="I91" s="43"/>
-      <c r="J91" s="54"/>
-      <c r="K91" s="44"/>
-      <c r="L91" s="44"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="46"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="47"/>
+      <c r="L91" s="47"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A92" s="3" t="s">
@@ -5983,14 +5913,14 @@
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
-      <c r="J92" s="54"/>
-      <c r="K92" s="42">
+      <c r="G92" s="46"/>
+      <c r="H92" s="46"/>
+      <c r="I92" s="46"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="45">
         <v>200</v>
       </c>
-      <c r="L92" s="42">
+      <c r="L92" s="45">
         <f>I85*(H85-K92)</f>
         <v>0</v>
       </c>
@@ -6004,25 +5934,39 @@
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="44"/>
-      <c r="J93" s="54"/>
-      <c r="K93" s="44"/>
-      <c r="L93" s="44"/>
+      <c r="G93" s="47"/>
+      <c r="H93" s="47"/>
+      <c r="I93" s="47"/>
+      <c r="J93" s="53"/>
+      <c r="K93" s="47"/>
+      <c r="L93" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="S12:S16"/>
-    <mergeCell ref="S17:S22"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S26:S29"/>
-    <mergeCell ref="L84:L85"/>
-    <mergeCell ref="L86:L87"/>
-    <mergeCell ref="L88:L89"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="L92:L93"/>
+  <mergeCells count="38">
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
     <mergeCell ref="G85:G93"/>
     <mergeCell ref="H85:H93"/>
     <mergeCell ref="I85:I93"/>
@@ -6032,56 +5976,15 @@
     <mergeCell ref="K88:K89"/>
     <mergeCell ref="K90:K91"/>
     <mergeCell ref="K92:K93"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="P35:Q36"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:R7"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="L84:L85"/>
+    <mergeCell ref="L86:L87"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="L92:L93"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
